--- a/research/traditional_assets/database/data/morocco/morocco_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_chemical_specialty.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1175575463200601</v>
+        <v>0.117211962171836</v>
       </c>
       <c r="C2">
-        <v>28.98027166266681</v>
+        <v>28.8066766852365</v>
       </c>
       <c r="D2">
-        <v>27.98027166266681</v>
+        <v>28.1156766852365</v>
       </c>
       <c r="E2">
-        <v>-11.3</v>
+        <v>-10.991</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3090000000000001</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1451,28 +1451,28 @@
         <v>1.45</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0155427</v>
       </c>
       <c r="N2">
-        <v>1.45</v>
+        <v>1.4344573</v>
       </c>
       <c r="O2">
-        <v>0.4639999999999999</v>
+        <v>0.459026336</v>
       </c>
       <c r="P2">
-        <v>0.9859999999999998</v>
+        <v>0.9754309639999998</v>
       </c>
       <c r="Q2">
-        <v>3.416</v>
+        <v>3.405430964</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1175575463200601</v>
+        <v>0.1180504264361979</v>
       </c>
       <c r="T2">
-        <v>0.935241381477821</v>
+        <v>0.9416652616738304</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>93.29138437980529</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.117211962171836</v>
+        <v>0.1168663780236117</v>
       </c>
       <c r="C3">
-        <v>28.8066766852365</v>
+        <v>28.63439861266873</v>
       </c>
       <c r="D3">
-        <v>28.1156766852365</v>
+        <v>28.25239861266873</v>
       </c>
       <c r="E3">
-        <v>-10.991</v>
+        <v>-10.682</v>
       </c>
       <c r="F3">
-        <v>0.3090000000000001</v>
+        <v>0.6180000000000001</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1533,28 +1533,28 @@
         <v>1.45</v>
       </c>
       <c r="M3">
-        <v>0.0155427</v>
+        <v>0.0310854</v>
       </c>
       <c r="N3">
-        <v>1.4344573</v>
+        <v>1.4189146</v>
       </c>
       <c r="O3">
-        <v>0.459026336</v>
+        <v>0.4540526719999999</v>
       </c>
       <c r="P3">
-        <v>0.9754309639999998</v>
+        <v>0.9648619279999997</v>
       </c>
       <c r="Q3">
-        <v>3.405430964</v>
+        <v>3.394861928</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1180504264361979</v>
+        <v>0.118553365330216</v>
       </c>
       <c r="T3">
-        <v>0.9416652616738304</v>
+        <v>0.9482202414656764</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>93.29138437980529</v>
+        <v>46.64569218990264</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1168663780236117</v>
+        <v>0.1165207938753876</v>
       </c>
       <c r="C4">
-        <v>28.63439861266873</v>
+        <v>28.4634567505207</v>
       </c>
       <c r="D4">
-        <v>28.25239861266873</v>
+        <v>28.39045675052069</v>
       </c>
       <c r="E4">
-        <v>-10.682</v>
+        <v>-10.373</v>
       </c>
       <c r="F4">
-        <v>0.6180000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1615,28 +1615,28 @@
         <v>1.45</v>
       </c>
       <c r="M4">
-        <v>0.0310854</v>
+        <v>0.0466281</v>
       </c>
       <c r="N4">
-        <v>1.4189146</v>
+        <v>1.4033719</v>
       </c>
       <c r="O4">
-        <v>0.4540526719999999</v>
+        <v>0.4490790079999999</v>
       </c>
       <c r="P4">
-        <v>0.9648619279999997</v>
+        <v>0.9542928919999998</v>
       </c>
       <c r="Q4">
-        <v>3.394861928</v>
+        <v>3.384292892</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.118553365330216</v>
+        <v>0.1190666740983377</v>
       </c>
       <c r="T4">
-        <v>0.9482202414656764</v>
+        <v>0.954910375480035</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>46.64569218990264</v>
+        <v>31.09712812660177</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1165207938753876</v>
+        <v>0.1161752097271633</v>
       </c>
       <c r="C5">
-        <v>28.4634567505207</v>
+        <v>28.29387078355679</v>
       </c>
       <c r="D5">
-        <v>28.39045675052069</v>
+        <v>28.52987078355679</v>
       </c>
       <c r="E5">
-        <v>-10.373</v>
+        <v>-10.064</v>
       </c>
       <c r="F5">
-        <v>0.927</v>
+        <v>1.236</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1697,28 +1697,28 @@
         <v>1.45</v>
       </c>
       <c r="M5">
-        <v>0.0466281</v>
+        <v>0.06217080000000001</v>
       </c>
       <c r="N5">
-        <v>1.4033719</v>
+        <v>1.3878292</v>
       </c>
       <c r="O5">
-        <v>0.4490790079999999</v>
+        <v>0.4441053439999999</v>
       </c>
       <c r="P5">
-        <v>0.9542928919999998</v>
+        <v>0.9437238559999998</v>
       </c>
       <c r="Q5">
-        <v>3.384292892</v>
+        <v>3.373723856</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1190666740983377</v>
+        <v>0.1195906767991285</v>
       </c>
       <c r="T5">
-        <v>0.954910375480035</v>
+        <v>0.9617398872863593</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.09712812660177</v>
+        <v>23.32284609495132</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1161752097271633</v>
+        <v>0.1158296255789392</v>
       </c>
       <c r="C6">
-        <v>28.29387078355679</v>
+        <v>28.12566078510503</v>
       </c>
       <c r="D6">
-        <v>28.52987078355679</v>
+        <v>28.67066078510504</v>
       </c>
       <c r="E6">
-        <v>-10.064</v>
+        <v>-9.755000000000001</v>
       </c>
       <c r="F6">
-        <v>1.236</v>
+        <v>1.545</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1779,28 +1779,28 @@
         <v>1.45</v>
       </c>
       <c r="M6">
-        <v>0.06217080000000001</v>
+        <v>0.0777135</v>
       </c>
       <c r="N6">
-        <v>1.3878292</v>
+        <v>1.3722865</v>
       </c>
       <c r="O6">
-        <v>0.4441053439999999</v>
+        <v>0.4391316799999999</v>
       </c>
       <c r="P6">
-        <v>0.9437238559999998</v>
+        <v>0.9331548199999998</v>
       </c>
       <c r="Q6">
-        <v>3.373723856</v>
+        <v>3.36315482</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1195906767991285</v>
+        <v>0.1201257111357254</v>
       </c>
       <c r="T6">
-        <v>0.9617398872863593</v>
+        <v>0.9687131782886063</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.32284609495132</v>
+        <v>18.65827687596106</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1158296255789392</v>
+        <v>0.1154840414307149</v>
       </c>
       <c r="C7">
-        <v>28.12566078510503</v>
+        <v>27.9588472266922</v>
       </c>
       <c r="D7">
-        <v>28.67066078510504</v>
+        <v>28.8128472266922</v>
       </c>
       <c r="E7">
-        <v>-9.755000000000001</v>
+        <v>-9.446</v>
       </c>
       <c r="F7">
-        <v>1.545</v>
+        <v>1.854</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1861,28 +1861,28 @@
         <v>1.45</v>
       </c>
       <c r="M7">
-        <v>0.0777135</v>
+        <v>0.09325620000000001</v>
       </c>
       <c r="N7">
-        <v>1.3722865</v>
+        <v>1.3567438</v>
       </c>
       <c r="O7">
-        <v>0.4391316799999999</v>
+        <v>0.434158016</v>
       </c>
       <c r="P7">
-        <v>0.9331548199999998</v>
+        <v>0.9225857839999998</v>
       </c>
       <c r="Q7">
-        <v>3.36315482</v>
+        <v>3.352585784</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1201257111357254</v>
+        <v>0.1206721291816117</v>
       </c>
       <c r="T7">
-        <v>0.9687131782886063</v>
+        <v>0.9758348371845179</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.65827687596106</v>
+        <v>15.54856406330088</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1154840414307149</v>
+        <v>0.1151384572824908</v>
       </c>
       <c r="C8">
-        <v>27.9588472266922</v>
+        <v>27.79345098796687</v>
       </c>
       <c r="D8">
-        <v>28.8128472266922</v>
+        <v>28.95645098796687</v>
       </c>
       <c r="E8">
-        <v>-9.446000000000002</v>
+        <v>-9.137</v>
       </c>
       <c r="F8">
-        <v>1.854</v>
+        <v>2.163</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1943,28 +1943,28 @@
         <v>1.45</v>
       </c>
       <c r="M8">
-        <v>0.0932562</v>
+        <v>0.1087989</v>
       </c>
       <c r="N8">
-        <v>1.3567438</v>
+        <v>1.3412011</v>
       </c>
       <c r="O8">
-        <v>0.434158016</v>
+        <v>0.4291843519999999</v>
       </c>
       <c r="P8">
-        <v>0.9225857839999998</v>
+        <v>0.9120167479999998</v>
       </c>
       <c r="Q8">
-        <v>3.352585784</v>
+        <v>3.342016748</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1206721291816117</v>
+        <v>0.1212302981532159</v>
       </c>
       <c r="T8">
-        <v>0.9758348371845179</v>
+        <v>0.9831096500351805</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.54856406330088</v>
+        <v>13.32734062568647</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1151384572824908</v>
+        <v>0.1148744731342666</v>
       </c>
       <c r="C9">
-        <v>27.79345098796687</v>
+        <v>27.59511479331788</v>
       </c>
       <c r="D9">
-        <v>28.95645098796687</v>
+        <v>29.06711479331788</v>
       </c>
       <c r="E9">
-        <v>-9.137</v>
+        <v>-8.827999999999999</v>
       </c>
       <c r="F9">
-        <v>2.163</v>
+        <v>2.472</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2025,45 +2025,45 @@
         <v>1.45</v>
       </c>
       <c r="M9">
-        <v>0.1087989</v>
+        <v>0.1280496</v>
       </c>
       <c r="N9">
-        <v>1.3412011</v>
+        <v>1.3219504</v>
       </c>
       <c r="O9">
-        <v>0.4291843519999999</v>
+        <v>0.4230241279999999</v>
       </c>
       <c r="P9">
-        <v>0.9120167479999998</v>
+        <v>0.8989262719999997</v>
       </c>
       <c r="Q9">
-        <v>3.342016748</v>
+        <v>3.328926272</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1212302981532159</v>
+        <v>0.1218006012328985</v>
       </c>
       <c r="T9">
-        <v>0.9831096500351805</v>
+        <v>0.9905426109912921</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.32</v>
       </c>
       <c r="W9">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.32734062568647</v>
+        <v>11.32373705189239</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1148744731342666</v>
+        <v>0.1145390889860424</v>
       </c>
       <c r="C10">
-        <v>27.59511479331788</v>
+        <v>27.42793583983003</v>
       </c>
       <c r="D10">
-        <v>29.06711479331788</v>
+        <v>29.20893583983003</v>
       </c>
       <c r="E10">
-        <v>-8.827999999999999</v>
+        <v>-8.519</v>
       </c>
       <c r="F10">
-        <v>2.472</v>
+        <v>2.781</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2107,28 +2107,28 @@
         <v>1.45</v>
       </c>
       <c r="M10">
-        <v>0.1280496</v>
+        <v>0.1440558</v>
       </c>
       <c r="N10">
-        <v>1.3219504</v>
+        <v>1.3059442</v>
       </c>
       <c r="O10">
-        <v>0.4230241279999999</v>
+        <v>0.4179021439999999</v>
       </c>
       <c r="P10">
-        <v>0.8989262719999997</v>
+        <v>0.8880420559999997</v>
       </c>
       <c r="Q10">
-        <v>3.328926272</v>
+        <v>3.318042056</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1218006012328985</v>
+        <v>0.1223834384462004</v>
       </c>
       <c r="T10">
-        <v>0.9905426109912921</v>
+        <v>0.9981389337266591</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.32373705189239</v>
+        <v>10.06554404612657</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1145390889860424</v>
+        <v>0.1143193048378182</v>
       </c>
       <c r="C11">
-        <v>27.42793583983003</v>
+        <v>27.21262711558489</v>
       </c>
       <c r="D11">
-        <v>29.20893583983003</v>
+        <v>29.30262711558489</v>
       </c>
       <c r="E11">
-        <v>-8.519</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="F11">
-        <v>2.781</v>
+        <v>3.09</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2189,45 +2189,45 @@
         <v>1.45</v>
       </c>
       <c r="M11">
-        <v>0.1440558</v>
+        <v>0.165315</v>
       </c>
       <c r="N11">
-        <v>1.3059442</v>
+        <v>1.284685</v>
       </c>
       <c r="O11">
-        <v>0.4179021439999999</v>
+        <v>0.4110991999999999</v>
       </c>
       <c r="P11">
-        <v>0.8880420559999997</v>
+        <v>0.8735857999999997</v>
       </c>
       <c r="Q11">
-        <v>3.318042056</v>
+        <v>3.3035858</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1223834384462004</v>
+        <v>0.1229792275975758</v>
       </c>
       <c r="T11">
-        <v>0.9981389337266591</v>
+        <v>1.005904063633923</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.32</v>
       </c>
       <c r="W11">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.06554404612657</v>
+        <v>8.771133895895712</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1143193048378182</v>
+        <v>0.113995480689594</v>
       </c>
       <c r="C12">
-        <v>27.21262711558489</v>
+        <v>27.04276974161353</v>
       </c>
       <c r="D12">
-        <v>29.30262711558489</v>
+        <v>29.44176974161353</v>
       </c>
       <c r="E12">
-        <v>-8.210000000000001</v>
+        <v>-7.901</v>
       </c>
       <c r="F12">
-        <v>3.09</v>
+        <v>3.399</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2271,28 +2271,28 @@
         <v>1.45</v>
       </c>
       <c r="M12">
-        <v>0.165315</v>
+        <v>0.1818465</v>
       </c>
       <c r="N12">
-        <v>1.284685</v>
+        <v>1.2681535</v>
       </c>
       <c r="O12">
-        <v>0.4110991999999999</v>
+        <v>0.4058091199999999</v>
       </c>
       <c r="P12">
-        <v>0.8735857999999997</v>
+        <v>0.8623443799999998</v>
       </c>
       <c r="Q12">
-        <v>3.3035858</v>
+        <v>3.29234438</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1229792275975758</v>
+        <v>0.1235884052692068</v>
       </c>
       <c r="T12">
-        <v>1.005904063633923</v>
+        <v>1.013843690842474</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.771133895895712</v>
+        <v>7.973758087177919</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.113995480689594</v>
+        <v>0.1137369365413698</v>
       </c>
       <c r="C13">
-        <v>27.04276974161353</v>
+        <v>26.84581478908816</v>
       </c>
       <c r="D13">
-        <v>29.44176974161353</v>
+        <v>29.55381478908816</v>
       </c>
       <c r="E13">
-        <v>-7.901</v>
+        <v>-7.592000000000001</v>
       </c>
       <c r="F13">
-        <v>3.399</v>
+        <v>3.708</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2353,45 +2353,45 @@
         <v>1.45</v>
       </c>
       <c r="M13">
-        <v>0.1818465</v>
+        <v>0.2013444</v>
       </c>
       <c r="N13">
-        <v>1.2681535</v>
+        <v>1.2486556</v>
       </c>
       <c r="O13">
-        <v>0.4058091199999999</v>
+        <v>0.3995697919999999</v>
       </c>
       <c r="P13">
-        <v>0.8623443799999998</v>
+        <v>0.8490858079999999</v>
       </c>
       <c r="Q13">
-        <v>3.29234438</v>
+        <v>3.279085808</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1235884052692068</v>
+        <v>0.1242114278879203</v>
       </c>
       <c r="T13">
-        <v>1.013843690842474</v>
+        <v>1.021963764123946</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.32</v>
       </c>
       <c r="W13">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.973758087177919</v>
+        <v>7.201590905930335</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1137369365413698</v>
+        <v>0.1134185523931456</v>
       </c>
       <c r="C14">
-        <v>26.84581478908816</v>
+        <v>26.67596988506969</v>
       </c>
       <c r="D14">
-        <v>29.55381478908816</v>
+        <v>29.69296988506969</v>
       </c>
       <c r="E14">
-        <v>-7.592000000000001</v>
+        <v>-7.283</v>
       </c>
       <c r="F14">
-        <v>3.708</v>
+        <v>4.017</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -2435,28 +2435,28 @@
         <v>1.45</v>
       </c>
       <c r="M14">
-        <v>0.2013444</v>
+        <v>0.2181231</v>
       </c>
       <c r="N14">
-        <v>1.2486556</v>
+        <v>1.2318769</v>
       </c>
       <c r="O14">
-        <v>0.3995697919999999</v>
+        <v>0.3942006079999999</v>
       </c>
       <c r="P14">
-        <v>0.8490858079999999</v>
+        <v>0.8376762919999997</v>
       </c>
       <c r="Q14">
-        <v>3.279085808</v>
+        <v>3.267676292</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1242114278879203</v>
+        <v>0.1248487728656846</v>
       </c>
       <c r="T14">
-        <v>1.021963764123946</v>
+        <v>1.030270505756717</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.201590905930335</v>
+        <v>6.647622374704923</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1134185523931456</v>
+        <v>0.1131001682449214</v>
       </c>
       <c r="C15">
-        <v>26.67596988506969</v>
+        <v>26.50744161302584</v>
       </c>
       <c r="D15">
-        <v>29.69296988506969</v>
+        <v>29.83344161302584</v>
       </c>
       <c r="E15">
-        <v>-7.283</v>
+        <v>-6.974</v>
       </c>
       <c r="F15">
-        <v>4.017</v>
+        <v>4.326000000000001</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2517,28 +2517,28 @@
         <v>1.45</v>
       </c>
       <c r="M15">
-        <v>0.2181231</v>
+        <v>0.2349018</v>
       </c>
       <c r="N15">
-        <v>1.2318769</v>
+        <v>1.2150982</v>
       </c>
       <c r="O15">
-        <v>0.3942006079999999</v>
+        <v>0.3888314239999999</v>
       </c>
       <c r="P15">
-        <v>0.8376762919999997</v>
+        <v>0.8262667759999998</v>
       </c>
       <c r="Q15">
-        <v>3.267676292</v>
+        <v>3.256266776</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1248487728656846</v>
+        <v>0.1255009398196761</v>
       </c>
       <c r="T15">
-        <v>1.030270505756717</v>
+        <v>1.038770427427459</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.647622374704923</v>
+        <v>6.172792205083144</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1131001682449214</v>
+        <v>0.1128837840966972</v>
       </c>
       <c r="C16">
-        <v>26.50744161302584</v>
+        <v>26.29467178159721</v>
       </c>
       <c r="D16">
-        <v>29.83344161302584</v>
+        <v>29.92967178159721</v>
       </c>
       <c r="E16">
-        <v>-6.974</v>
+        <v>-6.665</v>
       </c>
       <c r="F16">
-        <v>4.326000000000001</v>
+        <v>4.635000000000001</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -2599,45 +2599,45 @@
         <v>1.45</v>
       </c>
       <c r="M16">
-        <v>0.2349018</v>
+        <v>0.2563155</v>
       </c>
       <c r="N16">
-        <v>1.2150982</v>
+        <v>1.1936845</v>
       </c>
       <c r="O16">
-        <v>0.3888314239999999</v>
+        <v>0.3819790399999999</v>
       </c>
       <c r="P16">
-        <v>0.8262667759999998</v>
+        <v>0.8117054599999999</v>
       </c>
       <c r="Q16">
-        <v>3.256266776</v>
+        <v>3.24170546</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1255009398196761</v>
+        <v>0.1261684518784673</v>
       </c>
       <c r="T16">
-        <v>1.038770427427459</v>
+        <v>1.04747034725516</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.32</v>
       </c>
       <c r="W16">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.172792205083144</v>
+        <v>5.657090577823033</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1128837840966972</v>
+        <v>0.112572199948473</v>
       </c>
       <c r="C17">
-        <v>26.29467178159722</v>
+        <v>26.1253348643756</v>
       </c>
       <c r="D17">
-        <v>29.92967178159721</v>
+        <v>30.0693348643756</v>
       </c>
       <c r="E17">
-        <v>-6.665000000000001</v>
+        <v>-6.356</v>
       </c>
       <c r="F17">
-        <v>4.635</v>
+        <v>4.944000000000001</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -2681,28 +2681,28 @@
         <v>1.45</v>
       </c>
       <c r="M17">
-        <v>0.2563155</v>
+        <v>0.2734032000000001</v>
       </c>
       <c r="N17">
-        <v>1.1936845</v>
+        <v>1.1765968</v>
       </c>
       <c r="O17">
-        <v>0.3819790399999999</v>
+        <v>0.3765109759999999</v>
       </c>
       <c r="P17">
-        <v>0.8117054599999999</v>
+        <v>0.8000858239999997</v>
       </c>
       <c r="Q17">
-        <v>3.24170546</v>
+        <v>3.230085824</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1261684518784673</v>
+        <v>0.1268518570815155</v>
       </c>
       <c r="T17">
-        <v>1.04747034725516</v>
+        <v>1.056377408031139</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.657090577823034</v>
+        <v>5.303522416709092</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.112572199948473</v>
+        <v>0.1122606158002489</v>
       </c>
       <c r="C18">
-        <v>26.1253348643756</v>
+        <v>25.95730749874817</v>
       </c>
       <c r="D18">
-        <v>30.0693348643756</v>
+        <v>30.21030749874817</v>
       </c>
       <c r="E18">
-        <v>-6.356</v>
+        <v>-6.047</v>
       </c>
       <c r="F18">
-        <v>4.944000000000001</v>
+        <v>5.253000000000001</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -2763,28 +2763,28 @@
         <v>1.45</v>
       </c>
       <c r="M18">
-        <v>0.2734032000000001</v>
+        <v>0.2904909000000001</v>
       </c>
       <c r="N18">
-        <v>1.1765968</v>
+        <v>1.1595091</v>
       </c>
       <c r="O18">
-        <v>0.3765109759999999</v>
+        <v>0.3710429119999999</v>
       </c>
       <c r="P18">
-        <v>0.8000858239999997</v>
+        <v>0.7884661879999998</v>
       </c>
       <c r="Q18">
-        <v>3.230085824</v>
+        <v>3.218466188</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1268518570815155</v>
+        <v>0.1275517298798179</v>
       </c>
       <c r="T18">
-        <v>1.056377408031139</v>
+        <v>1.065499096777624</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.303522416709092</v>
+        <v>4.991550509843853</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1122606158002489</v>
+        <v>0.1119490316520246</v>
       </c>
       <c r="C19">
-        <v>25.95730749874817</v>
+        <v>25.79060818999798</v>
       </c>
       <c r="D19">
-        <v>30.21030749874817</v>
+        <v>30.35260818999798</v>
       </c>
       <c r="E19">
-        <v>-6.047</v>
+        <v>-5.738</v>
       </c>
       <c r="F19">
-        <v>5.253000000000001</v>
+        <v>5.562000000000001</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -2845,28 +2845,28 @@
         <v>1.45</v>
       </c>
       <c r="M19">
-        <v>0.2904909000000001</v>
+        <v>0.3075786000000001</v>
       </c>
       <c r="N19">
-        <v>1.1595091</v>
+        <v>1.1424214</v>
       </c>
       <c r="O19">
-        <v>0.3710429119999999</v>
+        <v>0.3655748479999999</v>
       </c>
       <c r="P19">
-        <v>0.7884661879999998</v>
+        <v>0.7768465519999999</v>
       </c>
       <c r="Q19">
-        <v>3.218466188</v>
+        <v>3.206846552</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1275517298798179</v>
+        <v>0.1282686727463715</v>
       </c>
       <c r="T19">
-        <v>1.065499096777624</v>
+        <v>1.074843265737437</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.991550509843853</v>
+        <v>4.714242148185861</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1119490316520247</v>
+        <v>0.1119604475038005</v>
       </c>
       <c r="C20">
-        <v>25.79060818999798</v>
+        <v>25.47637090867387</v>
       </c>
       <c r="D20">
-        <v>30.35260818999798</v>
+        <v>30.34737090867387</v>
       </c>
       <c r="E20">
-        <v>-5.738</v>
+        <v>-5.429</v>
       </c>
       <c r="F20">
-        <v>5.562</v>
+        <v>5.871</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -2927,45 +2927,45 @@
         <v>1.45</v>
       </c>
       <c r="M20">
-        <v>0.3075786</v>
+        <v>0.3393438</v>
       </c>
       <c r="N20">
-        <v>1.1424214</v>
+        <v>1.1106562</v>
       </c>
       <c r="O20">
-        <v>0.3655748479999999</v>
+        <v>0.355409984</v>
       </c>
       <c r="P20">
-        <v>0.7768465519999999</v>
+        <v>0.7552462159999997</v>
       </c>
       <c r="Q20">
-        <v>3.206846552</v>
+        <v>3.185246216</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1282686727463715</v>
+        <v>0.1290033179059265</v>
       </c>
       <c r="T20">
-        <v>1.074843265737437</v>
+        <v>1.084418154918481</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.32</v>
       </c>
       <c r="W20">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.714242148185861</v>
+        <v>4.272952681027324</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1119604475038005</v>
+        <v>0.1116658633555763</v>
       </c>
       <c r="C21">
-        <v>25.47637090867387</v>
+        <v>25.30309909858181</v>
       </c>
       <c r="D21">
-        <v>30.34737090867387</v>
+        <v>30.48309909858181</v>
       </c>
       <c r="E21">
-        <v>-5.429</v>
+        <v>-5.12</v>
       </c>
       <c r="F21">
-        <v>5.871</v>
+        <v>6.180000000000001</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -3009,28 +3009,28 @@
         <v>1.45</v>
       </c>
       <c r="M21">
-        <v>0.3393438</v>
+        <v>0.3572040000000001</v>
       </c>
       <c r="N21">
-        <v>1.1106562</v>
+        <v>1.092796</v>
       </c>
       <c r="O21">
-        <v>0.355409984</v>
+        <v>0.3496947199999999</v>
       </c>
       <c r="P21">
-        <v>0.7552462159999997</v>
+        <v>0.7431012799999998</v>
       </c>
       <c r="Q21">
-        <v>3.185246216</v>
+        <v>3.17310128</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1290033179059265</v>
+        <v>0.1297563291944703</v>
       </c>
       <c r="T21">
-        <v>1.084418154918481</v>
+        <v>1.09423241632905</v>
       </c>
       <c r="U21">
         <v>0.0578</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.272952681027324</v>
+        <v>4.059305046975956</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1116658633555763</v>
+        <v>0.1118710792073521</v>
       </c>
       <c r="C22">
-        <v>25.30309909858181</v>
+        <v>24.89941901735216</v>
       </c>
       <c r="D22">
-        <v>30.48309909858181</v>
+        <v>30.38841901735216</v>
       </c>
       <c r="E22">
-        <v>-5.12</v>
+        <v>-4.811</v>
       </c>
       <c r="F22">
-        <v>6.180000000000001</v>
+        <v>6.489000000000001</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -3091,45 +3091,45 @@
         <v>1.45</v>
       </c>
       <c r="M22">
-        <v>0.3572040000000001</v>
+        <v>0.3977757000000001</v>
       </c>
       <c r="N22">
-        <v>1.092796</v>
+        <v>1.0522243</v>
       </c>
       <c r="O22">
-        <v>0.3496947199999999</v>
+        <v>0.336711776</v>
       </c>
       <c r="P22">
-        <v>0.7431012799999998</v>
+        <v>0.7155125239999998</v>
       </c>
       <c r="Q22">
-        <v>3.17310128</v>
+        <v>3.145512524</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1297563291944703</v>
+        <v>0.1305284040599393</v>
       </c>
       <c r="T22">
-        <v>1.09423241632905</v>
+        <v>1.104295140053812</v>
       </c>
       <c r="U22">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V22">
         <v>0.32</v>
       </c>
       <c r="W22">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.059305046975956</v>
+        <v>3.645270437585804</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1118710792073521</v>
+        <v>0.1120191750591279</v>
       </c>
       <c r="C23">
-        <v>24.89941901735216</v>
+        <v>24.52245684786762</v>
       </c>
       <c r="D23">
-        <v>30.38841901735216</v>
+        <v>30.32045684786762</v>
       </c>
       <c r="E23">
-        <v>-4.811000000000001</v>
+        <v>-4.502</v>
       </c>
       <c r="F23">
-        <v>6.489</v>
+        <v>6.798000000000001</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3173,45 +3173,45 @@
         <v>1.45</v>
       </c>
       <c r="M23">
-        <v>0.3977757</v>
+        <v>0.4357518000000001</v>
       </c>
       <c r="N23">
-        <v>1.0522243</v>
+        <v>1.0142482</v>
       </c>
       <c r="O23">
-        <v>0.336711776</v>
+        <v>0.3245594239999999</v>
       </c>
       <c r="P23">
-        <v>0.7155125239999998</v>
+        <v>0.6896887759999998</v>
       </c>
       <c r="Q23">
-        <v>3.145512524</v>
+        <v>3.119688776</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1305284040599393</v>
+        <v>0.1313202757168306</v>
       </c>
       <c r="T23">
-        <v>1.104295140053812</v>
+        <v>1.114615882335618</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.32</v>
       </c>
       <c r="W23">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.645270437585804</v>
+        <v>3.327582353073469</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1120191750591279</v>
+        <v>0.1117674309109037</v>
       </c>
       <c r="C24">
-        <v>24.52245684786762</v>
+        <v>24.32916542522975</v>
       </c>
       <c r="D24">
-        <v>30.32045684786762</v>
+        <v>30.43616542522975</v>
       </c>
       <c r="E24">
-        <v>-4.502</v>
+        <v>-4.193</v>
       </c>
       <c r="F24">
-        <v>6.798000000000001</v>
+        <v>7.107000000000001</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -3255,28 +3255,28 @@
         <v>1.45</v>
       </c>
       <c r="M24">
-        <v>0.4357518000000001</v>
+        <v>0.4555587000000001</v>
       </c>
       <c r="N24">
-        <v>1.0142482</v>
+        <v>0.9944412999999996</v>
       </c>
       <c r="O24">
-        <v>0.3245594239999999</v>
+        <v>0.3182212159999999</v>
       </c>
       <c r="P24">
-        <v>0.6896887759999998</v>
+        <v>0.6762200839999997</v>
       </c>
       <c r="Q24">
-        <v>3.119688776</v>
+        <v>3.106220084</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1313202757168306</v>
+        <v>0.1321327154687061</v>
       </c>
       <c r="T24">
-        <v>1.114615882335618</v>
+        <v>1.125204695845524</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.327582353073469</v>
+        <v>3.182904859461579</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1117674309109037</v>
+        <v>0.1115156867626795</v>
       </c>
       <c r="C25">
-        <v>24.32916542522975</v>
+        <v>24.13676051717264</v>
       </c>
       <c r="D25">
-        <v>30.43616542522975</v>
+        <v>30.55276051717264</v>
       </c>
       <c r="E25">
-        <v>-4.193</v>
+        <v>-3.883999999999999</v>
       </c>
       <c r="F25">
-        <v>7.107000000000001</v>
+        <v>7.416000000000001</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3337,28 +3337,28 @@
         <v>1.45</v>
       </c>
       <c r="M25">
-        <v>0.4555587000000001</v>
+        <v>0.4753656000000001</v>
       </c>
       <c r="N25">
-        <v>0.9944412999999996</v>
+        <v>0.9746343999999996</v>
       </c>
       <c r="O25">
-        <v>0.3182212159999999</v>
+        <v>0.3118830079999999</v>
       </c>
       <c r="P25">
-        <v>0.6762200839999997</v>
+        <v>0.6627513919999997</v>
       </c>
       <c r="Q25">
-        <v>3.106220084</v>
+        <v>3.092751392</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1321327154687061</v>
+        <v>0.132966535214052</v>
       </c>
       <c r="T25">
-        <v>1.125204695845524</v>
+        <v>1.136072162342532</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.182904859461579</v>
+        <v>3.050283823650679</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1115156867626795</v>
+        <v>0.1125899426144553</v>
       </c>
       <c r="C26">
-        <v>24.13676051717264</v>
+        <v>23.33634698260893</v>
       </c>
       <c r="D26">
-        <v>30.55276051717264</v>
+        <v>30.06134698260893</v>
       </c>
       <c r="E26">
-        <v>-3.884</v>
+        <v>-3.575</v>
       </c>
       <c r="F26">
-        <v>7.416</v>
+        <v>7.725000000000001</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3419,45 +3419,45 @@
         <v>1.45</v>
       </c>
       <c r="M26">
-        <v>0.4753656000000001</v>
+        <v>0.5554275000000001</v>
       </c>
       <c r="N26">
-        <v>0.9746343999999997</v>
+        <v>0.8945724999999997</v>
       </c>
       <c r="O26">
-        <v>0.3118830079999999</v>
+        <v>0.2862631999999999</v>
       </c>
       <c r="P26">
-        <v>0.6627513919999998</v>
+        <v>0.6083092999999997</v>
       </c>
       <c r="Q26">
-        <v>3.092751392</v>
+        <v>3.0383093</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.132966535214052</v>
+        <v>0.1338225901526071</v>
       </c>
       <c r="T26">
-        <v>1.136072162342532</v>
+        <v>1.147229427946127</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.32</v>
       </c>
       <c r="W26">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.05028382365068</v>
+        <v>2.610601743701922</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1125899426144553</v>
+        <v>0.1123912384662311</v>
       </c>
       <c r="C27">
-        <v>23.33634698260893</v>
+        <v>23.11704818781598</v>
       </c>
       <c r="D27">
-        <v>30.06134698260893</v>
+        <v>30.15104818781598</v>
       </c>
       <c r="E27">
-        <v>-3.575</v>
+        <v>-3.266</v>
       </c>
       <c r="F27">
-        <v>7.725000000000001</v>
+        <v>8.034000000000001</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3501,28 +3501,28 @@
         <v>1.45</v>
       </c>
       <c r="M27">
-        <v>0.5554275000000001</v>
+        <v>0.5776446000000001</v>
       </c>
       <c r="N27">
-        <v>0.8945724999999997</v>
+        <v>0.8723553999999997</v>
       </c>
       <c r="O27">
-        <v>0.2862631999999999</v>
+        <v>0.2791537279999999</v>
       </c>
       <c r="P27">
-        <v>0.6083092999999997</v>
+        <v>0.5932016719999997</v>
       </c>
       <c r="Q27">
-        <v>3.0383093</v>
+        <v>3.023201672</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1338225901526071</v>
+        <v>0.1347017817111231</v>
       </c>
       <c r="T27">
-        <v>1.147229427946127</v>
+        <v>1.158688241268738</v>
       </c>
       <c r="U27">
         <v>0.07190000000000001</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.610601743701922</v>
+        <v>2.510193984328771</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1123912384662311</v>
+        <v>0.1129085743180069</v>
       </c>
       <c r="C28">
-        <v>23.11704818781598</v>
+        <v>22.57561562081996</v>
       </c>
       <c r="D28">
-        <v>30.15104818781598</v>
+        <v>29.91861562081996</v>
       </c>
       <c r="E28">
-        <v>-3.266</v>
+        <v>-2.956999999999999</v>
       </c>
       <c r="F28">
-        <v>8.034000000000001</v>
+        <v>8.343000000000002</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3583,45 +3583,45 @@
         <v>1.45</v>
       </c>
       <c r="M28">
-        <v>0.5776446000000001</v>
+        <v>0.6323994000000002</v>
       </c>
       <c r="N28">
-        <v>0.8723553999999997</v>
+        <v>0.8176005999999996</v>
       </c>
       <c r="O28">
-        <v>0.2791537279999999</v>
+        <v>0.2616321919999999</v>
       </c>
       <c r="P28">
-        <v>0.5932016719999997</v>
+        <v>0.5559684079999997</v>
       </c>
       <c r="Q28">
-        <v>3.023201672</v>
+        <v>2.985968408</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1347017817111231</v>
+        <v>0.1356050607095985</v>
       </c>
       <c r="T28">
-        <v>1.158688241268738</v>
+        <v>1.17046099468238</v>
       </c>
       <c r="U28">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.32</v>
       </c>
       <c r="W28">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.510193984328771</v>
+        <v>2.292854800304996</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1129085743180069</v>
+        <v>0.1127363901697827</v>
       </c>
       <c r="C29">
-        <v>22.57561562081996</v>
+        <v>22.34357691696473</v>
       </c>
       <c r="D29">
-        <v>29.91861562081996</v>
+        <v>29.99557691696473</v>
       </c>
       <c r="E29">
-        <v>-2.956999999999999</v>
+        <v>-2.648</v>
       </c>
       <c r="F29">
-        <v>8.343000000000002</v>
+        <v>8.652000000000001</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3665,28 +3665,28 @@
         <v>1.45</v>
       </c>
       <c r="M29">
-        <v>0.6323994000000002</v>
+        <v>0.6558216000000001</v>
       </c>
       <c r="N29">
-        <v>0.8176005999999996</v>
+        <v>0.7941783999999996</v>
       </c>
       <c r="O29">
-        <v>0.2616321919999999</v>
+        <v>0.2541370879999999</v>
       </c>
       <c r="P29">
-        <v>0.5559684079999997</v>
+        <v>0.5400413119999997</v>
       </c>
       <c r="Q29">
-        <v>2.985968408</v>
+        <v>2.970041312</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1356050607095985</v>
+        <v>0.1365334307913649</v>
       </c>
       <c r="T29">
-        <v>1.17046099468238</v>
+        <v>1.182560769024178</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.292854800304996</v>
+        <v>2.210967128865532</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1127363901697827</v>
+        <v>0.1125642060215585</v>
       </c>
       <c r="C30">
-        <v>22.34357691696473</v>
+        <v>22.11193517777101</v>
       </c>
       <c r="D30">
-        <v>29.99557691696473</v>
+        <v>30.07293517777101</v>
       </c>
       <c r="E30">
-        <v>-2.648</v>
+        <v>-2.338999999999999</v>
       </c>
       <c r="F30">
-        <v>8.652000000000001</v>
+        <v>8.961000000000002</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3747,28 +3747,28 @@
         <v>1.45</v>
       </c>
       <c r="M30">
-        <v>0.6558216000000001</v>
+        <v>0.6792438000000002</v>
       </c>
       <c r="N30">
-        <v>0.7941783999999996</v>
+        <v>0.7707561999999996</v>
       </c>
       <c r="O30">
-        <v>0.2541370879999999</v>
+        <v>0.2466419839999999</v>
       </c>
       <c r="P30">
-        <v>0.5400413119999997</v>
+        <v>0.5241142159999996</v>
       </c>
       <c r="Q30">
-        <v>2.970041312</v>
+        <v>2.954114216</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1365334307913649</v>
+        <v>0.1374879521430402</v>
       </c>
       <c r="T30">
-        <v>1.182560769024178</v>
+        <v>1.19500138207983</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.210967128865532</v>
+        <v>2.134726883042583</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1125642060215585</v>
+        <v>0.1123920218733343</v>
       </c>
       <c r="C31">
-        <v>22.11193517777102</v>
+        <v>21.88069348248258</v>
       </c>
       <c r="D31">
-        <v>30.07293517777101</v>
+        <v>30.15069348248258</v>
       </c>
       <c r="E31">
-        <v>-2.339</v>
+        <v>-2.030000000000001</v>
       </c>
       <c r="F31">
-        <v>8.961</v>
+        <v>9.27</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -3829,28 +3829,28 @@
         <v>1.45</v>
       </c>
       <c r="M31">
-        <v>0.6792438000000001</v>
+        <v>0.702666</v>
       </c>
       <c r="N31">
-        <v>0.7707561999999997</v>
+        <v>0.7473339999999997</v>
       </c>
       <c r="O31">
-        <v>0.2466419839999999</v>
+        <v>0.2391468799999999</v>
       </c>
       <c r="P31">
-        <v>0.5241142159999997</v>
+        <v>0.5081871199999998</v>
       </c>
       <c r="Q31">
-        <v>2.954114216</v>
+        <v>2.93818712</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1374879521430402</v>
+        <v>0.1384697455333348</v>
       </c>
       <c r="T31">
-        <v>1.19500138207983</v>
+        <v>1.207797441222786</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.134726883042583</v>
+        <v>2.063569320274497</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1123920218733343</v>
+        <v>0.1152131977251101</v>
       </c>
       <c r="C32">
-        <v>21.88069348248258</v>
+        <v>20.34627222031959</v>
       </c>
       <c r="D32">
-        <v>30.15069348248258</v>
+        <v>28.9252722203196</v>
       </c>
       <c r="E32">
-        <v>-2.030000000000001</v>
+        <v>-1.721</v>
       </c>
       <c r="F32">
-        <v>9.27</v>
+        <v>9.579000000000001</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -3911,45 +3911,45 @@
         <v>1.45</v>
       </c>
       <c r="M32">
-        <v>0.702666</v>
+        <v>0.86211</v>
       </c>
       <c r="N32">
-        <v>0.7473339999999997</v>
+        <v>0.5878899999999997</v>
       </c>
       <c r="O32">
-        <v>0.2391468799999999</v>
+        <v>0.1881247999999999</v>
       </c>
       <c r="P32">
-        <v>0.5081871199999998</v>
+        <v>0.3997651999999998</v>
       </c>
       <c r="Q32">
-        <v>2.93818712</v>
+        <v>2.8297652</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1384697455333348</v>
+        <v>0.1394799967030582</v>
       </c>
       <c r="T32">
-        <v>1.207797441222786</v>
+        <v>1.220964400630755</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V32">
         <v>0.32</v>
       </c>
       <c r="W32">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.063569320274497</v>
+        <v>1.681919940610827</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1152131977251101</v>
+        <v>0.1151375735768859</v>
       </c>
       <c r="C33">
-        <v>20.34627222031959</v>
+        <v>20.06882003719537</v>
       </c>
       <c r="D33">
-        <v>28.9252722203196</v>
+        <v>28.95682003719537</v>
       </c>
       <c r="E33">
-        <v>-1.721</v>
+        <v>-1.411999999999999</v>
       </c>
       <c r="F33">
-        <v>9.579000000000001</v>
+        <v>9.888000000000002</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3993,28 +3993,28 @@
         <v>1.45</v>
       </c>
       <c r="M33">
-        <v>0.86211</v>
+        <v>0.8899200000000002</v>
       </c>
       <c r="N33">
-        <v>0.5878899999999997</v>
+        <v>0.5600799999999996</v>
       </c>
       <c r="O33">
-        <v>0.1881247999999999</v>
+        <v>0.1792255999999999</v>
       </c>
       <c r="P33">
-        <v>0.3997651999999998</v>
+        <v>0.3808543999999997</v>
       </c>
       <c r="Q33">
-        <v>2.8297652</v>
+        <v>2.8108544</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1394799967030582</v>
+        <v>0.1405199611424794</v>
       </c>
       <c r="T33">
-        <v>1.220964400630755</v>
+        <v>1.234518623550724</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.681919940610827</v>
+        <v>1.629359942466738</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1151375735768859</v>
+        <v>0.1150619494286618</v>
       </c>
       <c r="C34">
-        <v>20.06882003719537</v>
+        <v>19.79143674548408</v>
       </c>
       <c r="D34">
-        <v>28.95682003719537</v>
+        <v>28.98843674548409</v>
       </c>
       <c r="E34">
-        <v>-1.411999999999999</v>
+        <v>-1.103</v>
       </c>
       <c r="F34">
-        <v>9.888000000000002</v>
+        <v>10.197</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -4075,28 +4075,28 @@
         <v>1.45</v>
       </c>
       <c r="M34">
-        <v>0.8899200000000002</v>
+        <v>0.91773</v>
       </c>
       <c r="N34">
-        <v>0.5600799999999996</v>
+        <v>0.5322699999999997</v>
       </c>
       <c r="O34">
-        <v>0.1792255999999999</v>
+        <v>0.1703263999999999</v>
       </c>
       <c r="P34">
-        <v>0.3808543999999997</v>
+        <v>0.3619435999999998</v>
       </c>
       <c r="Q34">
-        <v>2.8108544</v>
+        <v>2.7919436</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1405199611424794</v>
+        <v>0.1415909692965101</v>
       </c>
       <c r="T34">
-        <v>1.234518623550724</v>
+        <v>1.248477450139945</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.629359942466738</v>
+        <v>1.579985398755625</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1150619494286618</v>
+        <v>0.1149863252804376</v>
       </c>
       <c r="C35">
-        <v>19.79143674548408</v>
+        <v>19.51412257109113</v>
       </c>
       <c r="D35">
-        <v>28.98843674548409</v>
+        <v>29.02012257109113</v>
       </c>
       <c r="E35">
-        <v>-1.103</v>
+        <v>-0.7939999999999987</v>
       </c>
       <c r="F35">
-        <v>10.197</v>
+        <v>10.506</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -4157,28 +4157,28 @@
         <v>1.45</v>
       </c>
       <c r="M35">
-        <v>0.91773</v>
+        <v>0.9455400000000002</v>
       </c>
       <c r="N35">
-        <v>0.5322699999999997</v>
+        <v>0.5044599999999996</v>
       </c>
       <c r="O35">
-        <v>0.1703263999999999</v>
+        <v>0.1614271999999999</v>
       </c>
       <c r="P35">
-        <v>0.3619435999999998</v>
+        <v>0.3430327999999997</v>
       </c>
       <c r="Q35">
-        <v>2.7919436</v>
+        <v>2.7730328</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1415909692965101</v>
+        <v>0.1426944322430873</v>
       </c>
       <c r="T35">
-        <v>1.248477450139945</v>
+        <v>1.262859271474294</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.579985398755625</v>
+        <v>1.533515239968695</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1149863252804376</v>
+        <v>0.1305512811655872</v>
       </c>
       <c r="C36">
-        <v>19.51412257109113</v>
+        <v>13.87544588197841</v>
       </c>
       <c r="D36">
-        <v>29.02012257109113</v>
+        <v>23.69044588197841</v>
       </c>
       <c r="E36">
-        <v>-0.7939999999999987</v>
+        <v>-0.4849999999999994</v>
       </c>
       <c r="F36">
-        <v>10.506</v>
+        <v>10.815</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -4239,45 +4239,45 @@
         <v>1.45</v>
       </c>
       <c r="M36">
-        <v>0.9455400000000002</v>
+        <v>1.587642</v>
       </c>
       <c r="N36">
-        <v>0.5044599999999996</v>
+        <v>-0.1376420000000007</v>
       </c>
       <c r="O36">
-        <v>0.1614271999999999</v>
+        <v>-0.04404544000000023</v>
       </c>
       <c r="P36">
-        <v>0.3430327999999997</v>
+        <v>-0.09359656000000048</v>
       </c>
       <c r="Q36">
-        <v>2.7730328</v>
+        <v>2.33640344</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1426944322430873</v>
+        <v>0.1449037883005548</v>
       </c>
       <c r="T36">
-        <v>1.262859271474294</v>
+        <v>1.291654587330638</v>
       </c>
       <c r="U36">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.32</v>
+        <v>0.2922573224946177</v>
       </c>
       <c r="W36">
-        <v>0.06119999999999999</v>
+        <v>0.1038966250577901</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.533515239968695</v>
+        <v>0.9133041327956802</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1305512811655872</v>
+        <v>0.1315612811655872</v>
       </c>
       <c r="C37">
-        <v>13.87544588197841</v>
+        <v>13.2874464312286</v>
       </c>
       <c r="D37">
-        <v>23.69044588197841</v>
+        <v>23.4114464312286</v>
       </c>
       <c r="E37">
-        <v>-0.4849999999999994</v>
+        <v>-0.1759999999999984</v>
       </c>
       <c r="F37">
-        <v>10.815</v>
+        <v>11.124</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -4321,37 +4321,37 @@
         <v>1.45</v>
       </c>
       <c r="M37">
-        <v>1.587642</v>
+        <v>1.633003200000001</v>
       </c>
       <c r="N37">
-        <v>-0.1376420000000007</v>
+        <v>-0.1830032000000008</v>
       </c>
       <c r="O37">
-        <v>-0.04404544000000023</v>
+        <v>-0.05856102400000026</v>
       </c>
       <c r="P37">
-        <v>-0.09359656000000048</v>
+        <v>-0.1244421760000005</v>
       </c>
       <c r="Q37">
-        <v>2.33640344</v>
+        <v>2.305557824</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1449037883005548</v>
+        <v>0.146452284992751</v>
       </c>
       <c r="T37">
-        <v>1.291654587330638</v>
+        <v>1.311836690257679</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.2922573224946177</v>
+        <v>0.2841390635364339</v>
       </c>
       <c r="W37">
-        <v>0.1038966250577901</v>
+        <v>0.1050883854728515</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9133041327956802</v>
+        <v>0.8879345735513557</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1315612811655872</v>
+        <v>0.1325712811655872</v>
       </c>
       <c r="C38">
-        <v>13.2874464312286</v>
+        <v>12.705941973787</v>
       </c>
       <c r="D38">
-        <v>23.4114464312286</v>
+        <v>23.138941973787</v>
       </c>
       <c r="E38">
-        <v>-0.1760000000000002</v>
+        <v>0.1329999999999991</v>
       </c>
       <c r="F38">
-        <v>11.124</v>
+        <v>11.433</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -4403,37 +4403,37 @@
         <v>1.45</v>
       </c>
       <c r="M38">
-        <v>1.6330032</v>
+        <v>1.6783644</v>
       </c>
       <c r="N38">
-        <v>-0.1830032000000006</v>
+        <v>-0.2283644000000005</v>
       </c>
       <c r="O38">
-        <v>-0.05856102400000019</v>
+        <v>-0.07307660800000015</v>
       </c>
       <c r="P38">
-        <v>-0.1244421760000004</v>
+        <v>-0.1552877920000003</v>
       </c>
       <c r="Q38">
-        <v>2.305557824</v>
+        <v>2.274712208</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.146452284992751</v>
+        <v>0.1480499403100962</v>
       </c>
       <c r="T38">
-        <v>1.311836690257679</v>
+        <v>1.332659494864944</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.2841390635364339</v>
+        <v>0.2764596293868005</v>
       </c>
       <c r="W38">
-        <v>0.1050883854728515</v>
+        <v>0.1062157264060177</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8879345735513559</v>
+        <v>0.8639363418337517</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1325712811655872</v>
+        <v>0.1335812811655872</v>
       </c>
       <c r="C39">
-        <v>12.705941973787</v>
+        <v>12.13070831800976</v>
       </c>
       <c r="D39">
-        <v>23.138941973787</v>
+        <v>22.87270831800976</v>
       </c>
       <c r="E39">
-        <v>0.1329999999999991</v>
+        <v>0.4420000000000002</v>
       </c>
       <c r="F39">
-        <v>11.433</v>
+        <v>11.742</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -4485,37 +4485,37 @@
         <v>1.45</v>
       </c>
       <c r="M39">
-        <v>1.6783644</v>
+        <v>1.7237256</v>
       </c>
       <c r="N39">
-        <v>-0.2283644000000005</v>
+        <v>-0.2737256000000006</v>
       </c>
       <c r="O39">
-        <v>-0.07307660800000015</v>
+        <v>-0.08759219200000018</v>
       </c>
       <c r="P39">
-        <v>-0.1552877920000003</v>
+        <v>-0.1861334080000004</v>
       </c>
       <c r="Q39">
-        <v>2.274712208</v>
+        <v>2.243866592</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1480499403100962</v>
+        <v>0.1496991328957429</v>
       </c>
       <c r="T39">
-        <v>1.332659494864944</v>
+        <v>1.354154002846636</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.2764596293868005</v>
+        <v>0.2691843759818847</v>
       </c>
       <c r="W39">
-        <v>0.1062157264060177</v>
+        <v>0.1072837336058593</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8639363418337517</v>
+        <v>0.8412011749433898</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1335812811655872</v>
+        <v>0.1345912811655872</v>
       </c>
       <c r="C40">
-        <v>12.13070831800976</v>
+        <v>11.56153147296449</v>
       </c>
       <c r="D40">
-        <v>22.87270831800976</v>
+        <v>22.61253147296449</v>
       </c>
       <c r="E40">
-        <v>0.4420000000000002</v>
+        <v>0.7510000000000012</v>
       </c>
       <c r="F40">
-        <v>11.742</v>
+        <v>12.051</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -4567,37 +4567,37 @@
         <v>1.45</v>
       </c>
       <c r="M40">
-        <v>1.7237256</v>
+        <v>1.7690868</v>
       </c>
       <c r="N40">
-        <v>-0.2737256000000006</v>
+        <v>-0.3190868000000007</v>
       </c>
       <c r="O40">
-        <v>-0.08759219200000018</v>
+        <v>-0.1021077760000002</v>
       </c>
       <c r="P40">
-        <v>-0.1861334080000004</v>
+        <v>-0.2169790240000005</v>
       </c>
       <c r="Q40">
-        <v>2.243866592</v>
+        <v>2.213020976</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1496991328957429</v>
+        <v>0.1514023973694437</v>
       </c>
       <c r="T40">
-        <v>1.354154002846636</v>
+        <v>1.376353248794942</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.2691843759818847</v>
+        <v>0.2622822124951697</v>
       </c>
       <c r="W40">
-        <v>0.1072837336058593</v>
+        <v>0.1082969712057091</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8412011749433898</v>
+        <v>0.8196319140474053</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1345912811655872</v>
+        <v>0.1591752081174486</v>
       </c>
       <c r="C41">
-        <v>11.56153147296449</v>
+        <v>6.349300588906056</v>
       </c>
       <c r="D41">
-        <v>22.61253147296449</v>
+        <v>17.70930058890606</v>
       </c>
       <c r="E41">
-        <v>0.7510000000000012</v>
+        <v>1.06</v>
       </c>
       <c r="F41">
-        <v>12.051</v>
+        <v>12.36</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -4649,45 +4649,45 @@
         <v>1.45</v>
       </c>
       <c r="M41">
-        <v>1.7690868</v>
+        <v>2.481888000000001</v>
       </c>
       <c r="N41">
-        <v>-0.3190868000000007</v>
+        <v>-1.031888000000001</v>
       </c>
       <c r="O41">
-        <v>-0.1021077760000002</v>
+        <v>-0.3302041600000002</v>
       </c>
       <c r="P41">
-        <v>-0.2169790240000005</v>
+        <v>-0.7016838400000005</v>
       </c>
       <c r="Q41">
-        <v>2.213020976</v>
+        <v>1.72831616</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1514023973694437</v>
+        <v>0.1564523155787034</v>
       </c>
       <c r="T41">
-        <v>1.376353248794942</v>
+        <v>1.442170611909793</v>
       </c>
       <c r="U41">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.2622822124951697</v>
+        <v>0.1869544475818408</v>
       </c>
       <c r="W41">
-        <v>0.1082969712057091</v>
+        <v>0.1632595469255664</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.8196319140474053</v>
+        <v>0.5842326486932526</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1591752081174486</v>
+        <v>0.1607252081174486</v>
       </c>
       <c r="C42">
-        <v>6.349300588906056</v>
+        <v>5.801454678922992</v>
       </c>
       <c r="D42">
-        <v>17.70930058890606</v>
+        <v>17.47045467892299</v>
       </c>
       <c r="E42">
-        <v>1.06</v>
+        <v>1.369000000000002</v>
       </c>
       <c r="F42">
-        <v>12.36</v>
+        <v>12.669</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -4731,37 +4731,37 @@
         <v>1.45</v>
       </c>
       <c r="M42">
-        <v>2.481888000000001</v>
+        <v>2.5439352</v>
       </c>
       <c r="N42">
-        <v>-1.031888000000001</v>
+        <v>-1.093935200000001</v>
       </c>
       <c r="O42">
-        <v>-0.3302041600000002</v>
+        <v>-0.3500592640000002</v>
       </c>
       <c r="P42">
-        <v>-0.7016838400000005</v>
+        <v>-0.7438759360000005</v>
       </c>
       <c r="Q42">
-        <v>1.72831616</v>
+        <v>1.686124064</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1564523155787034</v>
+        <v>0.1583277785546136</v>
       </c>
       <c r="T42">
-        <v>1.442170611909793</v>
+        <v>1.466614181603179</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1869544475818408</v>
+        <v>0.182394583006674</v>
       </c>
       <c r="W42">
-        <v>0.1632595469255664</v>
+        <v>0.1641751677322599</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5842326486932526</v>
+        <v>0.5699830718958563</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1607252081174486</v>
+        <v>0.1622752081174486</v>
       </c>
       <c r="C43">
-        <v>5.801454678922992</v>
+        <v>5.259965678130442</v>
       </c>
       <c r="D43">
-        <v>17.47045467892299</v>
+        <v>17.23796567813044</v>
       </c>
       <c r="E43">
-        <v>1.369000000000002</v>
+        <v>1.678000000000001</v>
       </c>
       <c r="F43">
-        <v>12.669</v>
+        <v>12.978</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -4813,37 +4813,37 @@
         <v>1.45</v>
       </c>
       <c r="M43">
-        <v>2.5439352</v>
+        <v>2.6059824</v>
       </c>
       <c r="N43">
-        <v>-1.093935200000001</v>
+        <v>-1.155982400000001</v>
       </c>
       <c r="O43">
-        <v>-0.3500592640000002</v>
+        <v>-0.3699143680000002</v>
       </c>
       <c r="P43">
-        <v>-0.7438759360000005</v>
+        <v>-0.7860680320000004</v>
       </c>
       <c r="Q43">
-        <v>1.686124064</v>
+        <v>1.643931968</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1583277785546136</v>
+        <v>0.1602679126676242</v>
       </c>
       <c r="T43">
-        <v>1.466614181603179</v>
+        <v>1.49190063301013</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.182394583006674</v>
+        <v>0.1780518548398484</v>
       </c>
       <c r="W43">
-        <v>0.1641751677322599</v>
+        <v>0.1650471875481584</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5699830718958563</v>
+        <v>0.5564120463745263</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1622752081174486</v>
+        <v>0.1638252081174486</v>
       </c>
       <c r="C44">
-        <v>5.259965678130444</v>
+        <v>4.724583134712139</v>
       </c>
       <c r="D44">
-        <v>17.23796567813044</v>
+        <v>17.01158313471214</v>
       </c>
       <c r="E44">
-        <v>1.677999999999999</v>
+        <v>1.987</v>
       </c>
       <c r="F44">
-        <v>12.978</v>
+        <v>13.287</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -4895,37 +4895,37 @@
         <v>1.45</v>
       </c>
       <c r="M44">
-        <v>2.6059824</v>
+        <v>2.6680296</v>
       </c>
       <c r="N44">
-        <v>-1.155982400000001</v>
+        <v>-1.2180296</v>
       </c>
       <c r="O44">
-        <v>-0.3699143680000002</v>
+        <v>-0.3897694720000001</v>
       </c>
       <c r="P44">
-        <v>-0.7860680320000004</v>
+        <v>-0.8282601280000003</v>
       </c>
       <c r="Q44">
-        <v>1.643931968</v>
+        <v>1.601739872</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1602679126676242</v>
+        <v>0.1622761216617931</v>
       </c>
       <c r="T44">
-        <v>1.49190063301013</v>
+        <v>1.518074328326097</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1780518548398484</v>
+        <v>0.1739111140296194</v>
       </c>
       <c r="W44">
-        <v>0.1650471875481584</v>
+        <v>0.1658786483028524</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5564120463745263</v>
+        <v>0.5434722313425606</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1638252081174486</v>
+        <v>0.1653752081174486</v>
       </c>
       <c r="C45">
-        <v>4.724583134712139</v>
+        <v>4.195069582831847</v>
       </c>
       <c r="D45">
-        <v>17.01158313471214</v>
+        <v>16.79106958283185</v>
       </c>
       <c r="E45">
-        <v>1.987</v>
+        <v>2.296000000000001</v>
       </c>
       <c r="F45">
-        <v>13.287</v>
+        <v>13.596</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -4977,37 +4977,37 @@
         <v>1.45</v>
       </c>
       <c r="M45">
-        <v>2.6680296</v>
+        <v>2.7300768</v>
       </c>
       <c r="N45">
-        <v>-1.2180296</v>
+        <v>-1.280076800000001</v>
       </c>
       <c r="O45">
-        <v>-0.3897694720000001</v>
+        <v>-0.4096245760000002</v>
       </c>
       <c r="P45">
-        <v>-0.8282601280000003</v>
+        <v>-0.8704522240000004</v>
       </c>
       <c r="Q45">
-        <v>1.601739872</v>
+        <v>1.559547776</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1622761216617931</v>
+        <v>0.1643560524057537</v>
       </c>
       <c r="T45">
-        <v>1.518074328326097</v>
+        <v>1.545182798474778</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1739111140296194</v>
+        <v>0.1699585887107644</v>
       </c>
       <c r="W45">
-        <v>0.1658786483028524</v>
+        <v>0.1666723153868785</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5434722313425606</v>
+        <v>0.5311205897211388</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1653752081174486</v>
+        <v>0.1669252081174486</v>
       </c>
       <c r="C46">
-        <v>4.195069582831847</v>
+        <v>3.671199711746439</v>
       </c>
       <c r="D46">
-        <v>16.79106958283185</v>
+        <v>16.57619971174644</v>
       </c>
       <c r="E46">
-        <v>2.296000000000001</v>
+        <v>2.605</v>
       </c>
       <c r="F46">
-        <v>13.596</v>
+        <v>13.905</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -5059,37 +5059,37 @@
         <v>1.45</v>
       </c>
       <c r="M46">
-        <v>2.7300768</v>
+        <v>2.792124</v>
       </c>
       <c r="N46">
-        <v>-1.280076800000001</v>
+        <v>-1.342124000000001</v>
       </c>
       <c r="O46">
-        <v>-0.4096245760000002</v>
+        <v>-0.4294796800000002</v>
       </c>
       <c r="P46">
-        <v>-0.8704522240000004</v>
+        <v>-0.9126443200000003</v>
       </c>
       <c r="Q46">
-        <v>1.559547776</v>
+        <v>1.51735568</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1643560524057537</v>
+        <v>0.1665116169949492</v>
       </c>
       <c r="T46">
-        <v>1.545182798474778</v>
+        <v>1.573277031174319</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1699585887107644</v>
+        <v>0.1661817311838585</v>
       </c>
       <c r="W46">
-        <v>0.1666723153868785</v>
+        <v>0.1674307083782812</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5311205897211388</v>
+        <v>0.519317909949558</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1669252081174486</v>
+        <v>0.1684752081174486</v>
       </c>
       <c r="C47">
-        <v>3.671199711746439</v>
+        <v>3.152759597908535</v>
       </c>
       <c r="D47">
-        <v>16.57619971174644</v>
+        <v>16.36675959790854</v>
       </c>
       <c r="E47">
-        <v>2.605</v>
+        <v>2.914000000000001</v>
       </c>
       <c r="F47">
-        <v>13.905</v>
+        <v>14.214</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -5141,37 +5141,37 @@
         <v>1.45</v>
       </c>
       <c r="M47">
-        <v>2.792124</v>
+        <v>2.854171200000001</v>
       </c>
       <c r="N47">
-        <v>-1.342124000000001</v>
+        <v>-1.404171200000001</v>
       </c>
       <c r="O47">
-        <v>-0.4294796800000002</v>
+        <v>-0.4493347840000003</v>
       </c>
       <c r="P47">
-        <v>-0.9126443200000003</v>
+        <v>-0.9548364160000006</v>
       </c>
       <c r="Q47">
-        <v>1.51735568</v>
+        <v>1.475163584</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1665116169949492</v>
+        <v>0.1687470173096705</v>
       </c>
       <c r="T47">
-        <v>1.573277031174319</v>
+        <v>1.602411791010881</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1661817311838585</v>
+        <v>0.1625690848537747</v>
       </c>
       <c r="W47">
-        <v>0.1674307083782812</v>
+        <v>0.168156127761362</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.519317909949558</v>
+        <v>0.5080283901680458</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1684752081174486</v>
+        <v>0.1872717114849182</v>
       </c>
       <c r="C48">
-        <v>3.152759597908535</v>
+        <v>0.6692057689655009</v>
       </c>
       <c r="D48">
-        <v>16.36675959790854</v>
+        <v>14.1922057689655</v>
       </c>
       <c r="E48">
-        <v>2.914000000000001</v>
+        <v>3.223000000000001</v>
       </c>
       <c r="F48">
-        <v>14.214</v>
+        <v>14.523</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -5223,45 +5223,45 @@
         <v>1.45</v>
       </c>
       <c r="M48">
-        <v>2.854171200000001</v>
+        <v>3.4245234</v>
       </c>
       <c r="N48">
-        <v>-1.404171200000001</v>
+        <v>-1.974523400000001</v>
       </c>
       <c r="O48">
-        <v>-0.4493347840000003</v>
+        <v>-0.6318474880000002</v>
       </c>
       <c r="P48">
-        <v>-0.9548364160000006</v>
+        <v>-1.342675912</v>
       </c>
       <c r="Q48">
-        <v>1.475163584</v>
+        <v>1.087324088</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1687470173096705</v>
+        <v>0.1725696088956446</v>
       </c>
       <c r="T48">
-        <v>1.602411791010881</v>
+        <v>1.652232973855486</v>
       </c>
       <c r="U48">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1625690848537747</v>
+        <v>0.1354933068934497</v>
       </c>
       <c r="W48">
-        <v>0.168156127761362</v>
+        <v>0.2038506782345245</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.5080283901680458</v>
+        <v>0.4234165840420303</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1872717114849182</v>
+        <v>0.1891717114849182</v>
       </c>
       <c r="C49">
-        <v>0.6692057689655009</v>
+        <v>0.1721268886776581</v>
       </c>
       <c r="D49">
-        <v>14.1922057689655</v>
+        <v>14.00412688867766</v>
       </c>
       <c r="E49">
-        <v>3.223000000000001</v>
+        <v>3.532000000000002</v>
       </c>
       <c r="F49">
-        <v>14.523</v>
+        <v>14.832</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -5305,37 +5305,37 @@
         <v>1.45</v>
       </c>
       <c r="M49">
-        <v>3.4245234</v>
+        <v>3.497385600000001</v>
       </c>
       <c r="N49">
-        <v>-1.974523400000001</v>
+        <v>-2.047385600000001</v>
       </c>
       <c r="O49">
-        <v>-0.6318474880000002</v>
+        <v>-0.6551633920000003</v>
       </c>
       <c r="P49">
-        <v>-1.342675912</v>
+        <v>-1.392222208000001</v>
       </c>
       <c r="Q49">
-        <v>1.087324088</v>
+        <v>1.037777792</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1725696088956446</v>
+        <v>0.1750074859897917</v>
       </c>
       <c r="T49">
-        <v>1.652232973855486</v>
+        <v>1.684006684891169</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1354933068934497</v>
+        <v>0.1326705296665028</v>
       </c>
       <c r="W49">
-        <v>0.2038506782345245</v>
+        <v>0.2045162891046386</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4234165840420303</v>
+        <v>0.4145954052078213</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1891717114849182</v>
+        <v>0.1910717114849182</v>
       </c>
       <c r="C50">
-        <v>0.1721268886776599</v>
+        <v>-0.3200322468244305</v>
       </c>
       <c r="D50">
-        <v>14.00412688867766</v>
+        <v>13.82096775317557</v>
       </c>
       <c r="E50">
-        <v>3.532</v>
+        <v>3.840999999999999</v>
       </c>
       <c r="F50">
-        <v>14.832</v>
+        <v>15.141</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -5387,37 +5387,37 @@
         <v>1.45</v>
       </c>
       <c r="M50">
-        <v>3.4973856</v>
+        <v>3.5702478</v>
       </c>
       <c r="N50">
-        <v>-2.047385600000001</v>
+        <v>-2.1202478</v>
       </c>
       <c r="O50">
-        <v>-0.6551633920000002</v>
+        <v>-0.6784792960000001</v>
       </c>
       <c r="P50">
-        <v>-1.392222208</v>
+        <v>-1.441768504</v>
       </c>
       <c r="Q50">
-        <v>1.037777792</v>
+        <v>0.9882314959999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1750074859897917</v>
+        <v>0.1775409661072385</v>
       </c>
       <c r="T50">
-        <v>1.684006684891169</v>
+        <v>1.717026423810603</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1326705296665029</v>
+        <v>0.1299629678365742</v>
       </c>
       <c r="W50">
-        <v>0.2045162891046386</v>
+        <v>0.2051547321841358</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4145954052078215</v>
+        <v>0.4061342744892945</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1910717114849182</v>
+        <v>0.1929717114849182</v>
       </c>
       <c r="C51">
-        <v>-0.3200322468244305</v>
+        <v>-0.8074621805805879</v>
       </c>
       <c r="D51">
-        <v>13.82096775317557</v>
+        <v>13.64253781941941</v>
       </c>
       <c r="E51">
-        <v>3.840999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="F51">
-        <v>15.141</v>
+        <v>15.45</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -5469,37 +5469,37 @@
         <v>1.45</v>
       </c>
       <c r="M51">
-        <v>3.5702478</v>
+        <v>3.643110000000001</v>
       </c>
       <c r="N51">
-        <v>-2.1202478</v>
+        <v>-2.193110000000001</v>
       </c>
       <c r="O51">
-        <v>-0.6784792960000001</v>
+        <v>-0.7017952000000003</v>
       </c>
       <c r="P51">
-        <v>-1.441768504</v>
+        <v>-1.4913148</v>
       </c>
       <c r="Q51">
-        <v>0.9882314959999998</v>
+        <v>0.9386851999999997</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1775409661072385</v>
+        <v>0.1801757854293833</v>
       </c>
       <c r="T51">
-        <v>1.717026423810603</v>
+        <v>1.751366952286815</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1299629678365742</v>
+        <v>0.1273637084798427</v>
       </c>
       <c r="W51">
-        <v>0.2051547321841358</v>
+        <v>0.2057676375404531</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4061342744892945</v>
+        <v>0.3980115889995085</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1929717114849182</v>
+        <v>0.1948717114849182</v>
       </c>
       <c r="C52">
-        <v>-0.8074621805805879</v>
+        <v>-1.290343741332098</v>
       </c>
       <c r="D52">
-        <v>13.64253781941941</v>
+        <v>13.4686562586679</v>
       </c>
       <c r="E52">
-        <v>4.15</v>
+        <v>4.459000000000001</v>
       </c>
       <c r="F52">
-        <v>15.45</v>
+        <v>15.759</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -5551,37 +5551,37 @@
         <v>1.45</v>
       </c>
       <c r="M52">
-        <v>3.643110000000001</v>
+        <v>3.715972200000001</v>
       </c>
       <c r="N52">
-        <v>-2.193110000000001</v>
+        <v>-2.265972200000001</v>
       </c>
       <c r="O52">
-        <v>-0.7017952000000003</v>
+        <v>-0.7251111040000003</v>
       </c>
       <c r="P52">
-        <v>-1.4913148</v>
+        <v>-1.540861096000001</v>
       </c>
       <c r="Q52">
-        <v>0.9386851999999997</v>
+        <v>0.8891389039999993</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1801757854293833</v>
+        <v>0.1829181483973299</v>
       </c>
       <c r="T52">
-        <v>1.751366952286815</v>
+        <v>1.787109134986546</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1273637084798427</v>
+        <v>0.1248663808625909</v>
       </c>
       <c r="W52">
-        <v>0.2057676375404531</v>
+        <v>0.2063565073926011</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3980115889995085</v>
+        <v>0.3902074401955966</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1948717114849182</v>
+        <v>0.1967717114849182</v>
       </c>
       <c r="C53">
-        <v>-1.290343741332098</v>
+        <v>-1.768848654800776</v>
       </c>
       <c r="D53">
-        <v>13.4686562586679</v>
+        <v>13.29915134519923</v>
       </c>
       <c r="E53">
-        <v>4.459000000000001</v>
+        <v>4.768000000000001</v>
       </c>
       <c r="F53">
-        <v>15.759</v>
+        <v>16.068</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -5633,37 +5633,37 @@
         <v>1.45</v>
       </c>
       <c r="M53">
-        <v>3.715972200000001</v>
+        <v>3.7888344</v>
       </c>
       <c r="N53">
-        <v>-2.265972200000001</v>
+        <v>-2.338834400000001</v>
       </c>
       <c r="O53">
-        <v>-0.7251111040000003</v>
+        <v>-0.7484270080000002</v>
       </c>
       <c r="P53">
-        <v>-1.540861096000001</v>
+        <v>-1.590407392</v>
       </c>
       <c r="Q53">
-        <v>0.8891389039999993</v>
+        <v>0.8395926079999998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1829181483973299</v>
+        <v>0.1857747764889409</v>
       </c>
       <c r="T53">
-        <v>1.787109134986546</v>
+        <v>1.824340575298766</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1248663808625909</v>
+        <v>0.1224651043075411</v>
       </c>
       <c r="W53">
-        <v>0.2063565073926011</v>
+        <v>0.2069227284042818</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3902074401955966</v>
+        <v>0.3827034509610659</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1967717114849182</v>
+        <v>0.1986717114849182</v>
       </c>
       <c r="C54">
-        <v>-1.768848654800776</v>
+        <v>-2.243140109383409</v>
       </c>
       <c r="D54">
-        <v>13.29915134519923</v>
+        <v>13.13385989061659</v>
       </c>
       <c r="E54">
-        <v>4.768000000000001</v>
+        <v>5.077000000000002</v>
       </c>
       <c r="F54">
-        <v>16.068</v>
+        <v>16.377</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -5715,37 +5715,37 @@
         <v>1.45</v>
       </c>
       <c r="M54">
-        <v>3.7888344</v>
+        <v>3.861696600000001</v>
       </c>
       <c r="N54">
-        <v>-2.338834400000001</v>
+        <v>-2.411696600000001</v>
       </c>
       <c r="O54">
-        <v>-0.7484270080000002</v>
+        <v>-0.7717429120000003</v>
       </c>
       <c r="P54">
-        <v>-1.590407392</v>
+        <v>-1.639953688000001</v>
       </c>
       <c r="Q54">
-        <v>0.8395926079999998</v>
+        <v>0.7900463119999996</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1857747764889409</v>
+        <v>0.1887529632227482</v>
       </c>
       <c r="T54">
-        <v>1.824340575298766</v>
+        <v>1.863156332220016</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1224651043075411</v>
+        <v>0.1201544419621158</v>
       </c>
       <c r="W54">
-        <v>0.2069227284042818</v>
+        <v>0.2074675825853331</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3827034509610659</v>
+        <v>0.3754826311316118</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1986717114849182</v>
+        <v>0.2005717114849182</v>
       </c>
       <c r="C55">
-        <v>-2.243140109383409</v>
+        <v>-2.713373280178986</v>
       </c>
       <c r="D55">
-        <v>13.13385989061659</v>
+        <v>12.97262671982102</v>
       </c>
       <c r="E55">
-        <v>5.077000000000002</v>
+        <v>5.386000000000003</v>
       </c>
       <c r="F55">
-        <v>16.377</v>
+        <v>16.686</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -5797,37 +5797,37 @@
         <v>1.45</v>
       </c>
       <c r="M55">
-        <v>3.861696600000001</v>
+        <v>3.934558800000001</v>
       </c>
       <c r="N55">
-        <v>-2.411696600000001</v>
+        <v>-2.484558800000001</v>
       </c>
       <c r="O55">
-        <v>-0.7717429120000003</v>
+        <v>-0.7950588160000004</v>
       </c>
       <c r="P55">
-        <v>-1.639953688000001</v>
+        <v>-1.689499984000001</v>
       </c>
       <c r="Q55">
-        <v>0.7900463119999996</v>
+        <v>0.7405000159999995</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1887529632227482</v>
+        <v>0.1918606363362862</v>
       </c>
       <c r="T55">
-        <v>1.863156332220016</v>
+        <v>1.903659730746539</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1201544419621158</v>
+        <v>0.1179293597035581</v>
       </c>
       <c r="W55">
-        <v>0.2074675825853331</v>
+        <v>0.207992256981901</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3754826311316118</v>
+        <v>0.3685292490736189</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2005717114849182</v>
+        <v>0.2024717114849182</v>
       </c>
       <c r="C56">
-        <v>-2.713373280178986</v>
+        <v>-3.179695814885783</v>
       </c>
       <c r="D56">
-        <v>12.97262671982102</v>
+        <v>12.81530418511422</v>
       </c>
       <c r="E56">
-        <v>5.386000000000003</v>
+        <v>5.695</v>
       </c>
       <c r="F56">
-        <v>16.686</v>
+        <v>16.995</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -5879,37 +5879,37 @@
         <v>1.45</v>
       </c>
       <c r="M56">
-        <v>3.934558800000001</v>
+        <v>4.007421000000001</v>
       </c>
       <c r="N56">
-        <v>-2.484558800000001</v>
+        <v>-2.557421000000001</v>
       </c>
       <c r="O56">
-        <v>-0.7950588160000004</v>
+        <v>-0.8183747200000003</v>
       </c>
       <c r="P56">
-        <v>-1.689499984000001</v>
+        <v>-1.739046280000001</v>
       </c>
       <c r="Q56">
-        <v>0.7405000159999995</v>
+        <v>0.6909537199999995</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1918606363362862</v>
+        <v>0.1951064282548703</v>
       </c>
       <c r="T56">
-        <v>1.903659730746539</v>
+        <v>1.945963280318684</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1179293597035581</v>
+        <v>0.1157851895271297</v>
       </c>
       <c r="W56">
-        <v>0.207992256981901</v>
+        <v>0.2084978523095028</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3685292490736189</v>
+        <v>0.3618287172722805</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2024717114849182</v>
+        <v>0.2043717114849182</v>
       </c>
       <c r="C57">
-        <v>-3.179695814885783</v>
+        <v>-3.642248284766472</v>
       </c>
       <c r="D57">
-        <v>12.81530418511422</v>
+        <v>12.66175171523353</v>
       </c>
       <c r="E57">
-        <v>5.695</v>
+        <v>6.004000000000001</v>
       </c>
       <c r="F57">
-        <v>16.995</v>
+        <v>17.304</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -5961,37 +5961,37 @@
         <v>1.45</v>
       </c>
       <c r="M57">
-        <v>4.007421000000001</v>
+        <v>4.0802832</v>
       </c>
       <c r="N57">
-        <v>-2.557421000000001</v>
+        <v>-2.6302832</v>
       </c>
       <c r="O57">
-        <v>-0.8183747200000003</v>
+        <v>-0.8416906240000002</v>
       </c>
       <c r="P57">
-        <v>-1.739046280000001</v>
+        <v>-1.788592576</v>
       </c>
       <c r="Q57">
-        <v>0.6909537199999995</v>
+        <v>0.6414074239999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1951064282548703</v>
+        <v>0.1984997561697538</v>
       </c>
       <c r="T57">
-        <v>1.945963280318684</v>
+        <v>1.990189718507745</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1157851895271297</v>
+        <v>0.1137175968570024</v>
       </c>
       <c r="W57">
-        <v>0.2084978523095028</v>
+        <v>0.2089853906611188</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3618287172722805</v>
+        <v>0.3553674901781326</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2043717114849182</v>
+        <v>0.2062717114849182</v>
       </c>
       <c r="C58">
-        <v>-3.642248284766472</v>
+        <v>-4.101164603576377</v>
       </c>
       <c r="D58">
-        <v>12.66175171523353</v>
+        <v>12.51183539642363</v>
       </c>
       <c r="E58">
-        <v>6.004000000000001</v>
+        <v>6.313000000000002</v>
       </c>
       <c r="F58">
-        <v>17.304</v>
+        <v>17.613</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -6043,37 +6043,37 @@
         <v>1.45</v>
       </c>
       <c r="M58">
-        <v>4.0802832</v>
+        <v>4.153145400000001</v>
       </c>
       <c r="N58">
-        <v>-2.6302832</v>
+        <v>-2.703145400000001</v>
       </c>
       <c r="O58">
-        <v>-0.8416906240000002</v>
+        <v>-0.8650065280000003</v>
       </c>
       <c r="P58">
-        <v>-1.788592576</v>
+        <v>-1.838138872</v>
       </c>
       <c r="Q58">
-        <v>0.6414074239999998</v>
+        <v>0.5918611279999997</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1984997561697538</v>
+        <v>0.2020509132899806</v>
       </c>
       <c r="T58">
-        <v>1.990189718507745</v>
+        <v>2.036473200333507</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1137175968570024</v>
+        <v>0.1117225512981077</v>
       </c>
       <c r="W58">
-        <v>0.2089853906611188</v>
+        <v>0.2094558224039062</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3553674901781326</v>
+        <v>0.3491329728065864</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2062717114849182</v>
+        <v>0.2081717114849182</v>
       </c>
       <c r="C59">
-        <v>-4.101164603576377</v>
+        <v>-4.556572417079122</v>
       </c>
       <c r="D59">
-        <v>12.51183539642363</v>
+        <v>12.36542758292088</v>
       </c>
       <c r="E59">
-        <v>6.313000000000002</v>
+        <v>6.622000000000003</v>
       </c>
       <c r="F59">
-        <v>17.613</v>
+        <v>17.922</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -6125,37 +6125,37 @@
         <v>1.45</v>
       </c>
       <c r="M59">
-        <v>4.153145400000001</v>
+        <v>4.226007600000001</v>
       </c>
       <c r="N59">
-        <v>-2.703145400000001</v>
+        <v>-2.776007600000001</v>
       </c>
       <c r="O59">
-        <v>-0.8650065280000003</v>
+        <v>-0.8883224320000004</v>
       </c>
       <c r="P59">
-        <v>-1.838138872</v>
+        <v>-1.887685168000001</v>
       </c>
       <c r="Q59">
-        <v>0.5918611279999997</v>
+        <v>0.5423148319999993</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2020509132899806</v>
+        <v>0.2057711731302183</v>
       </c>
       <c r="T59">
-        <v>2.036473200333507</v>
+        <v>2.084960657484304</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1117225512981077</v>
+        <v>0.1097963004136575</v>
       </c>
       <c r="W59">
-        <v>0.2094558224039062</v>
+        <v>0.2099100323624596</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3491329728065864</v>
+        <v>0.3431134387926797</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2081717114849182</v>
+        <v>0.2100717114849182</v>
       </c>
       <c r="C60">
-        <v>-4.556572417079115</v>
+        <v>-5.008593465530947</v>
       </c>
       <c r="D60">
-        <v>12.36542758292089</v>
+        <v>12.22240653446906</v>
       </c>
       <c r="E60">
-        <v>6.622</v>
+        <v>6.931000000000001</v>
       </c>
       <c r="F60">
-        <v>17.922</v>
+        <v>18.231</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -6207,37 +6207,37 @@
         <v>1.45</v>
       </c>
       <c r="M60">
-        <v>4.2260076</v>
+        <v>4.2988698</v>
       </c>
       <c r="N60">
-        <v>-2.7760076</v>
+        <v>-2.848869800000001</v>
       </c>
       <c r="O60">
-        <v>-0.8883224320000001</v>
+        <v>-0.9116383360000002</v>
       </c>
       <c r="P60">
-        <v>-1.887685168</v>
+        <v>-1.937231464</v>
       </c>
       <c r="Q60">
-        <v>0.542314832</v>
+        <v>0.4927685359999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2057711731302182</v>
+        <v>0.2096729090602235</v>
       </c>
       <c r="T60">
-        <v>2.084960657484304</v>
+        <v>2.135813356447335</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1097963004136575</v>
+        <v>0.1079353461693583</v>
       </c>
       <c r="W60">
-        <v>0.2099100323624596</v>
+        <v>0.2103488453732653</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3431134387926799</v>
+        <v>0.3372979567792446</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2100717114849182</v>
+        <v>0.2119717114849182</v>
       </c>
       <c r="C61">
-        <v>-5.008593465530947</v>
+        <v>-5.457343921297294</v>
       </c>
       <c r="D61">
-        <v>12.22240653446906</v>
+        <v>12.0826560787027</v>
       </c>
       <c r="E61">
-        <v>6.931000000000001</v>
+        <v>7.239999999999998</v>
       </c>
       <c r="F61">
-        <v>18.231</v>
+        <v>18.54</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -6289,37 +6289,37 @@
         <v>1.45</v>
       </c>
       <c r="M61">
-        <v>4.2988698</v>
+        <v>4.371732</v>
       </c>
       <c r="N61">
-        <v>-2.848869800000001</v>
+        <v>-2.921732</v>
       </c>
       <c r="O61">
-        <v>-0.9116383360000002</v>
+        <v>-0.93495424</v>
       </c>
       <c r="P61">
-        <v>-1.937231464</v>
+        <v>-1.98677776</v>
       </c>
       <c r="Q61">
-        <v>0.4927685359999998</v>
+        <v>0.4432222400000003</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2096729090602235</v>
+        <v>0.2137697317867291</v>
       </c>
       <c r="T61">
-        <v>2.135813356447335</v>
+        <v>2.189208690358519</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1079353461693583</v>
+        <v>0.1061364237332023</v>
       </c>
       <c r="W61">
-        <v>0.2103488453732653</v>
+        <v>0.2107730312837109</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3372979567792446</v>
+        <v>0.3316763241662571</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2119717114849182</v>
+        <v>0.2138717114849182</v>
       </c>
       <c r="C62">
-        <v>-5.457343921297294</v>
+        <v>-5.90293470356939</v>
       </c>
       <c r="D62">
-        <v>12.0826560787027</v>
+        <v>11.94606529643061</v>
       </c>
       <c r="E62">
-        <v>7.239999999999998</v>
+        <v>7.548999999999999</v>
       </c>
       <c r="F62">
-        <v>18.54</v>
+        <v>18.849</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -6371,37 +6371,37 @@
         <v>1.45</v>
       </c>
       <c r="M62">
-        <v>4.371732</v>
+        <v>4.4445942</v>
       </c>
       <c r="N62">
-        <v>-2.921732</v>
+        <v>-2.9945942</v>
       </c>
       <c r="O62">
-        <v>-0.93495424</v>
+        <v>-0.9582701440000001</v>
       </c>
       <c r="P62">
-        <v>-1.98677776</v>
+        <v>-2.036324056</v>
       </c>
       <c r="Q62">
-        <v>0.4432222400000003</v>
+        <v>0.3936759439999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2137697317867291</v>
+        <v>0.2180766479863888</v>
       </c>
       <c r="T62">
-        <v>2.189208690358519</v>
+        <v>2.245342246521558</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1061364237332023</v>
+        <v>0.1043964823605269</v>
       </c>
       <c r="W62">
-        <v>0.2107730312837109</v>
+        <v>0.2111833094593878</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3316763241662571</v>
+        <v>0.3262390073766464</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2138717114849182</v>
+        <v>0.2157717114849182</v>
       </c>
       <c r="C63">
-        <v>-5.90293470356939</v>
+        <v>-6.345471771972871</v>
       </c>
       <c r="D63">
-        <v>11.94606529643061</v>
+        <v>11.81252822802713</v>
       </c>
       <c r="E63">
-        <v>7.548999999999999</v>
+        <v>7.858000000000001</v>
       </c>
       <c r="F63">
-        <v>18.849</v>
+        <v>19.158</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -6453,37 +6453,37 @@
         <v>1.45</v>
       </c>
       <c r="M63">
-        <v>4.4445942</v>
+        <v>4.5174564</v>
       </c>
       <c r="N63">
-        <v>-2.9945942</v>
+        <v>-3.067456400000001</v>
       </c>
       <c r="O63">
-        <v>-0.9582701440000001</v>
+        <v>-0.9815860480000003</v>
       </c>
       <c r="P63">
-        <v>-2.036324056</v>
+        <v>-2.085870352000001</v>
       </c>
       <c r="Q63">
-        <v>0.3936759439999999</v>
+        <v>0.3441296479999996</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2180766479863888</v>
+        <v>0.2226102439860306</v>
       </c>
       <c r="T63">
-        <v>2.245342246521558</v>
+        <v>2.304430200377388</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1043964823605269</v>
+        <v>0.1027126681289054</v>
       </c>
       <c r="W63">
-        <v>0.2111833094593878</v>
+        <v>0.2115803528552041</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3262390073766464</v>
+        <v>0.3209770879028295</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2157717114849182</v>
+        <v>0.2176717114849182</v>
       </c>
       <c r="C64">
-        <v>-6.345471771972871</v>
+        <v>-6.78505640070173</v>
       </c>
       <c r="D64">
-        <v>11.81252822802713</v>
+        <v>11.68194359929827</v>
       </c>
       <c r="E64">
-        <v>7.858000000000001</v>
+        <v>8.167000000000002</v>
       </c>
       <c r="F64">
-        <v>19.158</v>
+        <v>19.467</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6535,37 +6535,37 @@
         <v>1.45</v>
       </c>
       <c r="M64">
-        <v>4.5174564</v>
+        <v>4.590318600000001</v>
       </c>
       <c r="N64">
-        <v>-3.067456400000001</v>
+        <v>-3.140318600000001</v>
       </c>
       <c r="O64">
-        <v>-0.9815860480000003</v>
+        <v>-1.004901952</v>
       </c>
       <c r="P64">
-        <v>-2.085870352000001</v>
+        <v>-2.135416648000001</v>
       </c>
       <c r="Q64">
-        <v>0.3441296479999996</v>
+        <v>0.2945833519999996</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2226102439860306</v>
+        <v>0.2273888992288964</v>
       </c>
       <c r="T64">
-        <v>2.304430200377388</v>
+        <v>2.366712097684886</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1027126681289054</v>
+        <v>0.1010823083173355</v>
       </c>
       <c r="W64">
-        <v>0.2115803528552041</v>
+        <v>0.2119647916987723</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3209770879028295</v>
+        <v>0.3158822134916734</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2176717114849182</v>
+        <v>0.2195717114849182</v>
       </c>
       <c r="C65">
-        <v>-6.78505640070173</v>
+        <v>-7.22178543466819</v>
       </c>
       <c r="D65">
-        <v>11.68194359929827</v>
+        <v>11.55421456533181</v>
       </c>
       <c r="E65">
-        <v>8.167000000000002</v>
+        <v>8.476000000000003</v>
       </c>
       <c r="F65">
-        <v>19.467</v>
+        <v>19.776</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6617,37 +6617,37 @@
         <v>1.45</v>
       </c>
       <c r="M65">
-        <v>4.590318600000001</v>
+        <v>4.663180800000001</v>
       </c>
       <c r="N65">
-        <v>-3.140318600000001</v>
+        <v>-3.213180800000001</v>
       </c>
       <c r="O65">
-        <v>-1.004901952</v>
+        <v>-1.028217856</v>
       </c>
       <c r="P65">
-        <v>-2.135416648000001</v>
+        <v>-2.184962944000001</v>
       </c>
       <c r="Q65">
-        <v>0.2945833519999996</v>
+        <v>0.2450370559999993</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2273888992288964</v>
+        <v>0.2324330353185879</v>
       </c>
       <c r="T65">
-        <v>2.366712097684886</v>
+        <v>2.432454100398355</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1010823083173355</v>
+        <v>0.09950289724987713</v>
       </c>
       <c r="W65">
-        <v>0.2119647916987723</v>
+        <v>0.212337216828479</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3158822134916734</v>
+        <v>0.310946553905866</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2195717114849182</v>
+        <v>0.2214717114849182</v>
       </c>
       <c r="C66">
-        <v>-7.22178543466819</v>
+        <v>-7.655751529030031</v>
       </c>
       <c r="D66">
-        <v>11.55421456533181</v>
+        <v>11.42924847096997</v>
       </c>
       <c r="E66">
-        <v>8.476000000000003</v>
+        <v>8.785</v>
       </c>
       <c r="F66">
-        <v>19.776</v>
+        <v>20.085</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6699,37 +6699,37 @@
         <v>1.45</v>
       </c>
       <c r="M66">
-        <v>4.663180800000001</v>
+        <v>4.736043</v>
       </c>
       <c r="N66">
-        <v>-3.213180800000001</v>
+        <v>-3.286043000000001</v>
       </c>
       <c r="O66">
-        <v>-1.028217856</v>
+        <v>-1.05153376</v>
       </c>
       <c r="P66">
-        <v>-2.184962944000001</v>
+        <v>-2.23450924</v>
       </c>
       <c r="Q66">
-        <v>0.2450370559999993</v>
+        <v>0.1954907599999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2324330353185879</v>
+        <v>0.2377654077562619</v>
       </c>
       <c r="T66">
-        <v>2.432454100398355</v>
+        <v>2.501952788981165</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09950289724987713</v>
+        <v>0.09797208344603288</v>
       </c>
       <c r="W66">
-        <v>0.212337216828479</v>
+        <v>0.2126981827234254</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.310946553905866</v>
+        <v>0.3061627607688527</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2214717114849182</v>
+        <v>0.2233717114849182</v>
       </c>
       <c r="C67">
-        <v>-7.655751529030031</v>
+        <v>-8.087043373340421</v>
       </c>
       <c r="D67">
-        <v>11.42924847096997</v>
+        <v>11.30695662665958</v>
       </c>
       <c r="E67">
-        <v>8.785</v>
+        <v>9.094000000000001</v>
       </c>
       <c r="F67">
-        <v>20.085</v>
+        <v>20.394</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6781,37 +6781,37 @@
         <v>1.45</v>
       </c>
       <c r="M67">
-        <v>4.736043</v>
+        <v>4.808905200000001</v>
       </c>
       <c r="N67">
-        <v>-3.286043000000001</v>
+        <v>-3.358905200000001</v>
       </c>
       <c r="O67">
-        <v>-1.05153376</v>
+        <v>-1.074849664</v>
       </c>
       <c r="P67">
-        <v>-2.23450924</v>
+        <v>-2.284055536000001</v>
       </c>
       <c r="Q67">
-        <v>0.1954907599999998</v>
+        <v>0.1459444639999994</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2377654077562619</v>
+        <v>0.2434114491608578</v>
       </c>
       <c r="T67">
-        <v>2.501952788981165</v>
+        <v>2.575539635715905</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09797208344603288</v>
+        <v>0.0964876579392748</v>
       </c>
       <c r="W67">
-        <v>0.2126981827234254</v>
+        <v>0.213048210257919</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3061627607688527</v>
+        <v>0.3015239310602338</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2233717114849182</v>
+        <v>0.2252717114849182</v>
       </c>
       <c r="C68">
-        <v>-8.087043373340421</v>
+        <v>-8.515745901459784</v>
       </c>
       <c r="D68">
-        <v>11.30695662665958</v>
+        <v>11.18725409854022</v>
       </c>
       <c r="E68">
-        <v>9.094000000000001</v>
+        <v>9.403000000000002</v>
       </c>
       <c r="F68">
-        <v>20.394</v>
+        <v>20.703</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6863,37 +6863,37 @@
         <v>1.45</v>
       </c>
       <c r="M68">
-        <v>4.808905200000001</v>
+        <v>4.881767400000001</v>
       </c>
       <c r="N68">
-        <v>-3.358905200000001</v>
+        <v>-3.431767400000001</v>
       </c>
       <c r="O68">
-        <v>-1.074849664</v>
+        <v>-1.098165568</v>
       </c>
       <c r="P68">
-        <v>-2.284055536000001</v>
+        <v>-2.333601832000001</v>
       </c>
       <c r="Q68">
-        <v>0.1459444639999994</v>
+        <v>0.09639816799999901</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2434114491608578</v>
+        <v>0.249399674893005</v>
       </c>
       <c r="T68">
-        <v>2.575539635715905</v>
+        <v>2.65358629134366</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0964876579392748</v>
+        <v>0.09504754364167367</v>
       </c>
       <c r="W68">
-        <v>0.213048210257919</v>
+        <v>0.2133877892092934</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3015239310602338</v>
+        <v>0.2970235738802303</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2252717114849182</v>
+        <v>0.2271717114849182</v>
       </c>
       <c r="C69">
-        <v>-8.515745901459784</v>
+        <v>-8.941940488273803</v>
       </c>
       <c r="D69">
-        <v>11.18725409854022</v>
+        <v>11.0700595117262</v>
       </c>
       <c r="E69">
-        <v>9.403000000000002</v>
+        <v>9.712000000000003</v>
       </c>
       <c r="F69">
-        <v>20.703</v>
+        <v>21.012</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6945,37 +6945,37 @@
         <v>1.45</v>
       </c>
       <c r="M69">
-        <v>4.881767400000001</v>
+        <v>4.954629600000001</v>
       </c>
       <c r="N69">
-        <v>-3.431767400000001</v>
+        <v>-3.504629600000002</v>
       </c>
       <c r="O69">
-        <v>-1.098165568</v>
+        <v>-1.121481472000001</v>
       </c>
       <c r="P69">
-        <v>-2.333601832000001</v>
+        <v>-2.383148128000001</v>
       </c>
       <c r="Q69">
-        <v>0.09639816799999901</v>
+        <v>0.04685187199999907</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.249399674893005</v>
+        <v>0.2557621647334115</v>
       </c>
       <c r="T69">
-        <v>2.65358629134366</v>
+        <v>2.73651086294815</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09504754364167367</v>
+        <v>0.09364978564694316</v>
       </c>
       <c r="W69">
-        <v>0.2133877892092934</v>
+        <v>0.2137173805444508</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2970235738802303</v>
+        <v>0.2926555801466975</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2271717114849182</v>
+        <v>0.2290717114849182</v>
       </c>
       <c r="C70">
-        <v>-8.941940488273803</v>
+        <v>-9.365705134175036</v>
       </c>
       <c r="D70">
-        <v>11.0700595117262</v>
+        <v>10.95529486582497</v>
       </c>
       <c r="E70">
-        <v>9.712000000000003</v>
+        <v>10.021</v>
       </c>
       <c r="F70">
-        <v>21.012</v>
+        <v>21.321</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -7027,37 +7027,37 @@
         <v>1.45</v>
       </c>
       <c r="M70">
-        <v>4.954629600000001</v>
+        <v>5.027491800000001</v>
       </c>
       <c r="N70">
-        <v>-3.504629600000002</v>
+        <v>-3.577491800000001</v>
       </c>
       <c r="O70">
-        <v>-1.121481472000001</v>
+        <v>-1.144797376</v>
       </c>
       <c r="P70">
-        <v>-2.383148128000001</v>
+        <v>-2.432694424000001</v>
       </c>
       <c r="Q70">
-        <v>0.04685187199999907</v>
+        <v>-0.002694424000000861</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2557621647334115</v>
+        <v>0.262535137789328</v>
       </c>
       <c r="T70">
-        <v>2.73651086294815</v>
+        <v>2.824785406914219</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09364978564694316</v>
+        <v>0.09229254237669762</v>
       </c>
       <c r="W70">
-        <v>0.2137173805444508</v>
+        <v>0.2140374185075747</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2926555801466975</v>
+        <v>0.2884141949271801</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2290717114849182</v>
+        <v>0.2309717114849182</v>
       </c>
       <c r="C71">
-        <v>-9.365705134175036</v>
+        <v>-9.787114638187006</v>
       </c>
       <c r="D71">
-        <v>10.95529486582497</v>
+        <v>10.842885361813</v>
       </c>
       <c r="E71">
-        <v>10.021</v>
+        <v>10.33</v>
       </c>
       <c r="F71">
-        <v>21.321</v>
+        <v>21.63</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -7109,37 +7109,37 @@
         <v>1.45</v>
       </c>
       <c r="M71">
-        <v>5.027491800000001</v>
+        <v>5.100354000000001</v>
       </c>
       <c r="N71">
-        <v>-3.577491800000001</v>
+        <v>-3.650354000000001</v>
       </c>
       <c r="O71">
-        <v>-1.144797376</v>
+        <v>-1.16811328</v>
       </c>
       <c r="P71">
-        <v>-2.432694424000001</v>
+        <v>-2.482240720000001</v>
       </c>
       <c r="Q71">
-        <v>-0.002694424000000861</v>
+        <v>-0.0522407200000008</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.262535137789328</v>
+        <v>0.2697596423823055</v>
       </c>
       <c r="T71">
-        <v>2.824785406914219</v>
+        <v>2.918944920478026</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09229254237669762</v>
+        <v>0.09097407748560193</v>
       </c>
       <c r="W71">
-        <v>0.2140374185075747</v>
+        <v>0.2143483125288951</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2884141949271801</v>
+        <v>0.2842939921425061</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2309717114849182</v>
+        <v>0.2328717114849182</v>
       </c>
       <c r="C72">
-        <v>-9.787114638187006</v>
+        <v>-10.20624076053825</v>
       </c>
       <c r="D72">
-        <v>10.842885361813</v>
+        <v>10.73275923946175</v>
       </c>
       <c r="E72">
-        <v>10.33</v>
+        <v>10.639</v>
       </c>
       <c r="F72">
-        <v>21.63</v>
+        <v>21.939</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -7191,37 +7191,37 @@
         <v>1.45</v>
       </c>
       <c r="M72">
-        <v>5.100354000000001</v>
+        <v>5.173216200000001</v>
       </c>
       <c r="N72">
-        <v>-3.650354000000001</v>
+        <v>-3.723216200000002</v>
       </c>
       <c r="O72">
-        <v>-1.16811328</v>
+        <v>-1.191429184000001</v>
       </c>
       <c r="P72">
-        <v>-2.482240720000001</v>
+        <v>-2.531787016000001</v>
       </c>
       <c r="Q72">
-        <v>-0.0522407200000008</v>
+        <v>-0.1017870160000007</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2697596423823055</v>
+        <v>0.2774823886713506</v>
       </c>
       <c r="T72">
-        <v>2.918944920478026</v>
+        <v>3.019598193597959</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09097407748560193</v>
+        <v>0.08969275245059347</v>
       </c>
       <c r="W72">
-        <v>0.2143483125288951</v>
+        <v>0.2146504489721501</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2842939921425061</v>
+        <v>0.2802898514081046</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2328717114849182</v>
+        <v>0.2347717114849182</v>
       </c>
       <c r="C73">
-        <v>-10.20624076053825</v>
+        <v>-10.62315237542884</v>
       </c>
       <c r="D73">
-        <v>10.73275923946175</v>
+        <v>10.62484762457116</v>
       </c>
       <c r="E73">
-        <v>10.639</v>
+        <v>10.948</v>
       </c>
       <c r="F73">
-        <v>21.939</v>
+        <v>22.248</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -7273,37 +7273,37 @@
         <v>1.45</v>
       </c>
       <c r="M73">
-        <v>5.173216200000001</v>
+        <v>5.246078400000001</v>
       </c>
       <c r="N73">
-        <v>-3.723216200000001</v>
+        <v>-3.796078400000001</v>
       </c>
       <c r="O73">
-        <v>-1.191429184</v>
+        <v>-1.214745088</v>
       </c>
       <c r="P73">
-        <v>-2.531787016000001</v>
+        <v>-2.581333312000001</v>
       </c>
       <c r="Q73">
-        <v>-0.1017870160000007</v>
+        <v>-0.1513333120000007</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2774823886713505</v>
+        <v>0.2857567596953273</v>
       </c>
       <c r="T73">
-        <v>3.019598193597957</v>
+        <v>3.127440986226456</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08969275245059347</v>
+        <v>0.08844701977766857</v>
       </c>
       <c r="W73">
-        <v>0.2146504489721501</v>
+        <v>0.2149441927364258</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2802898514081046</v>
+        <v>0.2763969368052143</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2347717114849182</v>
+        <v>0.2366717114849182</v>
       </c>
       <c r="C74">
-        <v>-10.62315237542884</v>
+        <v>-11.03791561467281</v>
       </c>
       <c r="D74">
-        <v>10.62484762457116</v>
+        <v>10.51908438532719</v>
       </c>
       <c r="E74">
-        <v>10.948</v>
+        <v>11.257</v>
       </c>
       <c r="F74">
-        <v>22.248</v>
+        <v>22.557</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -7355,37 +7355,37 @@
         <v>1.45</v>
       </c>
       <c r="M74">
-        <v>5.246078400000001</v>
+        <v>5.3189406</v>
       </c>
       <c r="N74">
-        <v>-3.796078400000001</v>
+        <v>-3.868940600000001</v>
       </c>
       <c r="O74">
-        <v>-1.214745088</v>
+        <v>-1.238060992</v>
       </c>
       <c r="P74">
-        <v>-2.581333312000001</v>
+        <v>-2.630879608</v>
       </c>
       <c r="Q74">
-        <v>-0.1513333120000007</v>
+        <v>-0.2008796080000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2857567596953273</v>
+        <v>0.2946440470914505</v>
       </c>
       <c r="T74">
-        <v>3.127440986226456</v>
+        <v>3.243272133864472</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08844701977766857</v>
+        <v>0.08723541676701559</v>
       </c>
       <c r="W74">
-        <v>0.2149441927364258</v>
+        <v>0.2152298887263377</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2763969368052143</v>
+        <v>0.2726106773969237</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2366717114849182</v>
+        <v>0.2385717114849182</v>
       </c>
       <c r="C75">
-        <v>-11.03791561467281</v>
+        <v>-11.45059400284589</v>
       </c>
       <c r="D75">
-        <v>10.51908438532719</v>
+        <v>10.41540599715411</v>
       </c>
       <c r="E75">
-        <v>11.257</v>
+        <v>11.566</v>
       </c>
       <c r="F75">
-        <v>22.557</v>
+        <v>22.866</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7437,37 +7437,37 @@
         <v>1.45</v>
       </c>
       <c r="M75">
-        <v>5.3189406</v>
+        <v>5.3918028</v>
       </c>
       <c r="N75">
-        <v>-3.868940600000001</v>
+        <v>-3.9418028</v>
       </c>
       <c r="O75">
-        <v>-1.238060992</v>
+        <v>-1.261376896</v>
       </c>
       <c r="P75">
-        <v>-2.630879608</v>
+        <v>-2.680425904</v>
       </c>
       <c r="Q75">
-        <v>-0.2008796080000002</v>
+        <v>-0.2504259039999996</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2946440470914505</v>
+        <v>0.3042149719795832</v>
       </c>
       <c r="T75">
-        <v>3.243272133864472</v>
+        <v>3.368013369782337</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08723541676701559</v>
+        <v>0.08605655978367753</v>
       </c>
       <c r="W75">
-        <v>0.2152298887263377</v>
+        <v>0.2155078632030089</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2726106773969237</v>
+        <v>0.2689267493239923</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2385717114849182</v>
+        <v>0.2404717114849182</v>
       </c>
       <c r="C76">
-        <v>-11.45059400284589</v>
+        <v>-11.86124858451903</v>
       </c>
       <c r="D76">
-        <v>10.41540599715411</v>
+        <v>10.31375141548097</v>
       </c>
       <c r="E76">
-        <v>11.566</v>
+        <v>11.875</v>
       </c>
       <c r="F76">
-        <v>22.866</v>
+        <v>23.175</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7519,37 +7519,37 @@
         <v>1.45</v>
       </c>
       <c r="M76">
-        <v>5.3918028</v>
+        <v>5.464665</v>
       </c>
       <c r="N76">
-        <v>-3.9418028</v>
+        <v>-4.014665000000001</v>
       </c>
       <c r="O76">
-        <v>-1.261376896</v>
+        <v>-1.2846928</v>
       </c>
       <c r="P76">
-        <v>-2.680425904</v>
+        <v>-2.729972200000001</v>
       </c>
       <c r="Q76">
-        <v>-0.2504259039999996</v>
+        <v>-0.2999722000000005</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3042149719795832</v>
+        <v>0.3145515708587666</v>
       </c>
       <c r="T76">
-        <v>3.368013369782337</v>
+        <v>3.502733904573631</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08605655978367753</v>
+        <v>0.08490913898656183</v>
       </c>
       <c r="W76">
-        <v>0.2155078632030089</v>
+        <v>0.2157784250269687</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2689267493239923</v>
+        <v>0.2653410593330057</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2404717114849182</v>
+        <v>0.2423717114849182</v>
       </c>
       <c r="C77">
-        <v>-11.86124858451903</v>
+        <v>-12.2699380441131</v>
       </c>
       <c r="D77">
-        <v>10.31375141548097</v>
+        <v>10.2140619558869</v>
       </c>
       <c r="E77">
-        <v>11.875</v>
+        <v>12.184</v>
       </c>
       <c r="F77">
-        <v>23.175</v>
+        <v>23.484</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -7601,37 +7601,37 @@
         <v>1.45</v>
       </c>
       <c r="M77">
-        <v>5.464665</v>
+        <v>5.5375272</v>
       </c>
       <c r="N77">
-        <v>-4.014665000000001</v>
+        <v>-4.0875272</v>
       </c>
       <c r="O77">
-        <v>-1.2846928</v>
+        <v>-1.308008704</v>
       </c>
       <c r="P77">
-        <v>-2.729972200000001</v>
+        <v>-2.779518496</v>
       </c>
       <c r="Q77">
-        <v>-0.2999722000000005</v>
+        <v>-0.349518496</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3145515708587666</v>
+        <v>0.3257495529778819</v>
       </c>
       <c r="T77">
-        <v>3.502733904573631</v>
+        <v>3.648681150597533</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08490913898656183</v>
+        <v>0.08379191347358075</v>
       </c>
       <c r="W77">
-        <v>0.2157784250269687</v>
+        <v>0.2160418668029297</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2653410593330057</v>
+        <v>0.2618497296049399</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2423717114849182</v>
+        <v>0.2442717114849182</v>
       </c>
       <c r="C78">
-        <v>-12.2699380441131</v>
+        <v>-12.67671881886931</v>
       </c>
       <c r="D78">
-        <v>10.2140619558869</v>
+        <v>10.11628118113069</v>
       </c>
       <c r="E78">
-        <v>12.184</v>
+        <v>12.493</v>
       </c>
       <c r="F78">
-        <v>23.484</v>
+        <v>23.793</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -7683,37 +7683,37 @@
         <v>1.45</v>
       </c>
       <c r="M78">
-        <v>5.5375272</v>
+        <v>5.610389400000001</v>
       </c>
       <c r="N78">
-        <v>-4.0875272</v>
+        <v>-4.160389400000001</v>
       </c>
       <c r="O78">
-        <v>-1.308008704</v>
+        <v>-1.331324608000001</v>
       </c>
       <c r="P78">
-        <v>-2.779518496</v>
+        <v>-2.829064792000001</v>
       </c>
       <c r="Q78">
-        <v>-0.349518496</v>
+        <v>-0.3990647920000008</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3257495529778819</v>
+        <v>0.3379212726725724</v>
       </c>
       <c r="T78">
-        <v>3.648681150597533</v>
+        <v>3.807319461493077</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08379191347358075</v>
+        <v>0.08270370680509269</v>
       </c>
       <c r="W78">
-        <v>0.2160418668029297</v>
+        <v>0.2162984659353592</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2618497296049399</v>
+        <v>0.2584490837659146</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2442717114849182</v>
+        <v>0.2461717114849182</v>
       </c>
       <c r="C79">
-        <v>-12.67671881886931</v>
+        <v>-13.08164520539216</v>
       </c>
       <c r="D79">
-        <v>10.11628118113069</v>
+        <v>10.02035479460784</v>
       </c>
       <c r="E79">
-        <v>12.493</v>
+        <v>12.802</v>
       </c>
       <c r="F79">
-        <v>23.793</v>
+        <v>24.102</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -7765,37 +7765,37 @@
         <v>1.45</v>
       </c>
       <c r="M79">
-        <v>5.610389400000001</v>
+        <v>5.683251600000001</v>
       </c>
       <c r="N79">
-        <v>-4.160389400000001</v>
+        <v>-4.233251600000001</v>
       </c>
       <c r="O79">
-        <v>-1.331324608000001</v>
+        <v>-1.354640512</v>
       </c>
       <c r="P79">
-        <v>-2.829064792000001</v>
+        <v>-2.878611088</v>
       </c>
       <c r="Q79">
-        <v>-0.3990647920000008</v>
+        <v>-0.4486110880000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3379212726725724</v>
+        <v>0.3511995123395075</v>
       </c>
       <c r="T79">
-        <v>3.807319461493077</v>
+        <v>3.98037943701549</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08270370680509269</v>
+        <v>0.08164340287169405</v>
       </c>
       <c r="W79">
-        <v>0.2162984659353592</v>
+        <v>0.2165484856028546</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2584490837659146</v>
+        <v>0.255135633974044</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2461717114849182</v>
+        <v>0.2480717114849182</v>
       </c>
       <c r="C80">
-        <v>-13.08164520539216</v>
+        <v>-13.48476946018779</v>
       </c>
       <c r="D80">
-        <v>10.02035479460784</v>
+        <v>9.926230539812209</v>
       </c>
       <c r="E80">
-        <v>12.802</v>
+        <v>13.111</v>
       </c>
       <c r="F80">
-        <v>24.102</v>
+        <v>24.411</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -7847,37 +7847,37 @@
         <v>1.45</v>
       </c>
       <c r="M80">
-        <v>5.683251600000001</v>
+        <v>5.756113800000001</v>
       </c>
       <c r="N80">
-        <v>-4.233251600000001</v>
+        <v>-4.3061138</v>
       </c>
       <c r="O80">
-        <v>-1.354640512</v>
+        <v>-1.377956416</v>
       </c>
       <c r="P80">
-        <v>-2.878611088</v>
+        <v>-2.928157384</v>
       </c>
       <c r="Q80">
-        <v>-0.4486110880000003</v>
+        <v>-0.4981573840000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3511995123395075</v>
+        <v>0.3657423462604365</v>
       </c>
       <c r="T80">
-        <v>3.98037943701549</v>
+        <v>4.169921314968609</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08164340287169405</v>
+        <v>0.08060994207584983</v>
       </c>
       <c r="W80">
-        <v>0.2165484856028546</v>
+        <v>0.2167921756585146</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.255135633974044</v>
+        <v>0.2519060689870308</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2480717114849182</v>
+        <v>0.2499717114849182</v>
       </c>
       <c r="C81">
-        <v>-13.48476946018779</v>
+        <v>-13.88614189458861</v>
       </c>
       <c r="D81">
-        <v>9.926230539812209</v>
+        <v>9.833858105411389</v>
       </c>
       <c r="E81">
-        <v>13.111</v>
+        <v>13.42</v>
       </c>
       <c r="F81">
-        <v>24.411</v>
+        <v>24.72</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -7929,37 +7929,37 @@
         <v>1.45</v>
       </c>
       <c r="M81">
-        <v>5.756113800000001</v>
+        <v>5.828976000000001</v>
       </c>
       <c r="N81">
-        <v>-4.3061138</v>
+        <v>-4.378976000000002</v>
       </c>
       <c r="O81">
-        <v>-1.377956416</v>
+        <v>-1.401272320000001</v>
       </c>
       <c r="P81">
-        <v>-2.928157384</v>
+        <v>-2.977703680000001</v>
       </c>
       <c r="Q81">
-        <v>-0.4981573840000002</v>
+        <v>-0.547703680000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3657423462604365</v>
+        <v>0.3817394635734583</v>
       </c>
       <c r="T81">
-        <v>4.169921314968609</v>
+        <v>4.378417380717039</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08060994207584983</v>
+        <v>0.07960231779990171</v>
       </c>
       <c r="W81">
-        <v>0.2167921756585146</v>
+        <v>0.2170297734627832</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2519060689870308</v>
+        <v>0.2487572431246927</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2499717114849182</v>
+        <v>0.2518717114849183</v>
       </c>
       <c r="C82">
-        <v>-13.88614189458861</v>
+        <v>-14.28581096442671</v>
       </c>
       <c r="D82">
-        <v>9.833858105411389</v>
+        <v>9.743189035573293</v>
       </c>
       <c r="E82">
-        <v>13.42</v>
+        <v>13.729</v>
       </c>
       <c r="F82">
-        <v>24.72</v>
+        <v>25.029</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -8011,37 +8011,37 @@
         <v>1.45</v>
       </c>
       <c r="M82">
-        <v>5.828976000000001</v>
+        <v>5.901838200000001</v>
       </c>
       <c r="N82">
-        <v>-4.378976000000002</v>
+        <v>-4.451838200000001</v>
       </c>
       <c r="O82">
-        <v>-1.401272320000001</v>
+        <v>-1.424588224</v>
       </c>
       <c r="P82">
-        <v>-2.977703680000001</v>
+        <v>-3.027249976000001</v>
       </c>
       <c r="Q82">
-        <v>-0.547703680000001</v>
+        <v>-0.5972499760000005</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3817394635734583</v>
+        <v>0.3994204879720614</v>
       </c>
       <c r="T82">
-        <v>4.378417380717039</v>
+        <v>4.608860400754779</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07960231779990171</v>
+        <v>0.07861957313570539</v>
       </c>
       <c r="W82">
-        <v>0.2170297734627832</v>
+        <v>0.2172615046546007</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2487572431246927</v>
+        <v>0.2456861660490794</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2518717114849183</v>
+        <v>0.2537717114849182</v>
       </c>
       <c r="C83">
-        <v>-14.28581096442671</v>
+        <v>-14.68382335479179</v>
       </c>
       <c r="D83">
-        <v>9.743189035573293</v>
+        <v>9.654176645208217</v>
       </c>
       <c r="E83">
-        <v>13.729</v>
+        <v>14.038</v>
       </c>
       <c r="F83">
-        <v>25.029</v>
+        <v>25.338</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -8093,37 +8093,37 @@
         <v>1.45</v>
       </c>
       <c r="M83">
-        <v>5.901838200000001</v>
+        <v>5.974700400000001</v>
       </c>
       <c r="N83">
-        <v>-4.451838200000001</v>
+        <v>-4.524700400000002</v>
       </c>
       <c r="O83">
-        <v>-1.424588224</v>
+        <v>-1.447904128000001</v>
       </c>
       <c r="P83">
-        <v>-3.027249976000001</v>
+        <v>-3.076796272000001</v>
       </c>
       <c r="Q83">
-        <v>-0.5972499760000005</v>
+        <v>-0.6467962720000013</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3994204879720614</v>
+        <v>0.4190660706371759</v>
       </c>
       <c r="T83">
-        <v>4.608860400754779</v>
+        <v>4.864908200796711</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07861957313570539</v>
+        <v>0.07766079785356263</v>
       </c>
       <c r="W83">
-        <v>0.2172615046546007</v>
+        <v>0.21748758386613</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2456861660490794</v>
+        <v>0.2426899932923832</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2537717114849182</v>
+        <v>0.2556717114849182</v>
       </c>
       <c r="C84">
-        <v>-14.68382335479179</v>
+        <v>-15.08022406018516</v>
       </c>
       <c r="D84">
-        <v>9.654176645208217</v>
+        <v>9.566775939814846</v>
       </c>
       <c r="E84">
-        <v>14.038</v>
+        <v>14.347</v>
       </c>
       <c r="F84">
-        <v>25.338</v>
+        <v>25.64700000000001</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -8175,37 +8175,37 @@
         <v>1.45</v>
       </c>
       <c r="M84">
-        <v>5.974700400000001</v>
+        <v>6.047562600000002</v>
       </c>
       <c r="N84">
-        <v>-4.524700400000002</v>
+        <v>-4.597562600000002</v>
       </c>
       <c r="O84">
-        <v>-1.447904128000001</v>
+        <v>-1.471220032000001</v>
       </c>
       <c r="P84">
-        <v>-3.076796272000001</v>
+        <v>-3.126342568000001</v>
       </c>
       <c r="Q84">
-        <v>-0.6467962720000013</v>
+        <v>-0.6963425680000008</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4190660706371759</v>
+        <v>0.4410228983217158</v>
       </c>
       <c r="T84">
-        <v>4.864908200796711</v>
+        <v>5.151079271431812</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07766079785356263</v>
+        <v>0.0767251255902667</v>
       </c>
       <c r="W84">
-        <v>0.21748758386613</v>
+        <v>0.2177082153858151</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2426899932923832</v>
+        <v>0.2397660174695835</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2556717114849182</v>
+        <v>0.2575717114849182</v>
       </c>
       <c r="C85">
-        <v>-15.08022406018516</v>
+        <v>-15.47505646035888</v>
       </c>
       <c r="D85">
-        <v>9.566775939814846</v>
+        <v>9.480943539641123</v>
       </c>
       <c r="E85">
-        <v>14.347</v>
+        <v>14.656</v>
       </c>
       <c r="F85">
-        <v>25.64700000000001</v>
+        <v>25.956</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -8257,37 +8257,37 @@
         <v>1.45</v>
       </c>
       <c r="M85">
-        <v>6.047562600000002</v>
+        <v>6.120424800000001</v>
       </c>
       <c r="N85">
-        <v>-4.597562600000002</v>
+        <v>-4.670424800000001</v>
       </c>
       <c r="O85">
-        <v>-1.471220032000001</v>
+        <v>-1.494535936</v>
       </c>
       <c r="P85">
-        <v>-3.126342568000001</v>
+        <v>-3.175888864000001</v>
       </c>
       <c r="Q85">
-        <v>-0.6963425680000008</v>
+        <v>-0.7458888640000008</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4410228983217158</v>
+        <v>0.465724329466823</v>
       </c>
       <c r="T85">
-        <v>5.151079271431812</v>
+        <v>5.473021725896301</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0767251255902667</v>
+        <v>0.07581173123800163</v>
       </c>
       <c r="W85">
-        <v>0.2177082153858151</v>
+        <v>0.2179235937740792</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2397660174695835</v>
+        <v>0.2369116601187551</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2575717114849182</v>
+        <v>0.2594717114849182</v>
       </c>
       <c r="C86">
-        <v>-15.47505646035888</v>
+        <v>-15.86836239210871</v>
       </c>
       <c r="D86">
-        <v>9.480943539641123</v>
+        <v>9.396637607891286</v>
       </c>
       <c r="E86">
-        <v>14.656</v>
+        <v>14.965</v>
       </c>
       <c r="F86">
-        <v>25.956</v>
+        <v>26.265</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -8339,37 +8339,37 @@
         <v>1.45</v>
       </c>
       <c r="M86">
-        <v>6.1204248</v>
+        <v>6.193287000000001</v>
       </c>
       <c r="N86">
-        <v>-4.670424800000001</v>
+        <v>-4.743287</v>
       </c>
       <c r="O86">
-        <v>-1.494535936</v>
+        <v>-1.51785184</v>
       </c>
       <c r="P86">
-        <v>-3.175888864000001</v>
+        <v>-3.22543516</v>
       </c>
       <c r="Q86">
-        <v>-0.7458888640000008</v>
+        <v>-0.7954351599999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4657243294668227</v>
+        <v>0.4937192847646109</v>
       </c>
       <c r="T86">
-        <v>5.473021725896297</v>
+        <v>5.83788984095605</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07581173123800164</v>
+        <v>0.07491982851755455</v>
       </c>
       <c r="W86">
-        <v>0.2179235937740792</v>
+        <v>0.2181339044355607</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.236911660118755</v>
+        <v>0.234124464117358</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2594717114849182</v>
+        <v>0.2613717114849182</v>
       </c>
       <c r="C87">
-        <v>-15.86836239210871</v>
+        <v>-16.26018221727043</v>
       </c>
       <c r="D87">
-        <v>9.396637607891286</v>
+        <v>9.313817782729569</v>
       </c>
       <c r="E87">
-        <v>14.965</v>
+        <v>15.274</v>
       </c>
       <c r="F87">
-        <v>26.265</v>
+        <v>26.574</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -8421,37 +8421,37 @@
         <v>1.45</v>
       </c>
       <c r="M87">
-        <v>6.193287000000001</v>
+        <v>6.266149200000001</v>
       </c>
       <c r="N87">
-        <v>-4.743287</v>
+        <v>-4.816149200000002</v>
       </c>
       <c r="O87">
-        <v>-1.51785184</v>
+        <v>-1.541167744000001</v>
       </c>
       <c r="P87">
-        <v>-3.22543516</v>
+        <v>-3.274981456000001</v>
       </c>
       <c r="Q87">
-        <v>-0.7954351599999998</v>
+        <v>-0.8449814560000006</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4937192847646109</v>
+        <v>0.5257135193906546</v>
       </c>
       <c r="T87">
-        <v>5.83788984095605</v>
+        <v>6.254881972452911</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07491982851755455</v>
+        <v>0.0740486677208388</v>
       </c>
       <c r="W87">
-        <v>0.2181339044355607</v>
+        <v>0.2183393241514262</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.234124464117358</v>
+        <v>0.2314020866276212</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2613717114849182</v>
+        <v>0.2632717114849182</v>
       </c>
       <c r="C88">
-        <v>-16.26018221727043</v>
+        <v>-16.65055488715175</v>
       </c>
       <c r="D88">
-        <v>9.313817782729569</v>
+        <v>9.232445112848252</v>
       </c>
       <c r="E88">
-        <v>15.274</v>
+        <v>15.583</v>
       </c>
       <c r="F88">
-        <v>26.574</v>
+        <v>26.883</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -8503,37 +8503,37 @@
         <v>1.45</v>
       </c>
       <c r="M88">
-        <v>6.266149200000001</v>
+        <v>6.339011400000001</v>
       </c>
       <c r="N88">
-        <v>-4.816149200000002</v>
+        <v>-4.889011400000001</v>
       </c>
       <c r="O88">
-        <v>-1.541167744000001</v>
+        <v>-1.564483648</v>
       </c>
       <c r="P88">
-        <v>-3.274981456000001</v>
+        <v>-3.324527752000001</v>
       </c>
       <c r="Q88">
-        <v>-0.8449814560000006</v>
+        <v>-0.8945277520000006</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5257135193906546</v>
+        <v>0.5626299439591664</v>
       </c>
       <c r="T88">
-        <v>6.254881972452911</v>
+        <v>6.736026739564674</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0740486677208388</v>
+        <v>0.07319753360910501</v>
       </c>
       <c r="W88">
-        <v>0.2183393241514262</v>
+        <v>0.2185400215749731</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2314020866276212</v>
+        <v>0.2287422925284532</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2632717114849182</v>
+        <v>0.2651717114849182</v>
       </c>
       <c r="C89">
-        <v>-16.65055488715175</v>
+        <v>-17.03951800361591</v>
       </c>
       <c r="D89">
-        <v>9.232445112848252</v>
+        <v>9.15248199638409</v>
       </c>
       <c r="E89">
-        <v>15.583</v>
+        <v>15.892</v>
       </c>
       <c r="F89">
-        <v>26.883</v>
+        <v>27.192</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -8585,37 +8585,37 @@
         <v>1.45</v>
       </c>
       <c r="M89">
-        <v>6.339011400000001</v>
+        <v>6.411873600000001</v>
       </c>
       <c r="N89">
-        <v>-4.889011400000001</v>
+        <v>-4.961873600000001</v>
       </c>
       <c r="O89">
-        <v>-1.564483648</v>
+        <v>-1.587799552</v>
       </c>
       <c r="P89">
-        <v>-3.324527752000001</v>
+        <v>-3.374074048000001</v>
       </c>
       <c r="Q89">
-        <v>-0.8945277520000006</v>
+        <v>-0.9440740480000005</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5626299439591664</v>
+        <v>0.6056991059557637</v>
       </c>
       <c r="T89">
-        <v>6.736026739564674</v>
+        <v>7.297362301195064</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07319753360910501</v>
+        <v>0.07236574345445611</v>
       </c>
       <c r="W89">
-        <v>0.2185400215749731</v>
+        <v>0.2187361576934393</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2287422925284532</v>
+        <v>0.2261429482951753</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2651717114849182</v>
+        <v>0.2670717114849182</v>
       </c>
       <c r="C90">
-        <v>-17.03951800361591</v>
+        <v>-17.4271078770183</v>
       </c>
       <c r="D90">
-        <v>9.15248199638409</v>
+        <v>9.0738921229817</v>
       </c>
       <c r="E90">
-        <v>15.892</v>
+        <v>16.201</v>
       </c>
       <c r="F90">
-        <v>27.192</v>
+        <v>27.501</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -8667,37 +8667,37 @@
         <v>1.45</v>
       </c>
       <c r="M90">
-        <v>6.411873600000001</v>
+        <v>6.4847358</v>
       </c>
       <c r="N90">
-        <v>-4.961873600000001</v>
+        <v>-5.0347358</v>
       </c>
       <c r="O90">
-        <v>-1.587799552</v>
+        <v>-1.611115456</v>
       </c>
       <c r="P90">
-        <v>-3.374074048000001</v>
+        <v>-3.423620344</v>
       </c>
       <c r="Q90">
-        <v>-0.9440740480000005</v>
+        <v>-0.9936203439999995</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6056991059557637</v>
+        <v>0.656599024679015</v>
       </c>
       <c r="T90">
-        <v>7.297362301195064</v>
+        <v>7.96075887403098</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07236574345445611</v>
+        <v>0.0715526452133948</v>
       </c>
       <c r="W90">
-        <v>0.2187361576934393</v>
+        <v>0.2189278862586815</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2261429482951753</v>
+        <v>0.2236020162918588</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2670717114849182</v>
+        <v>0.2689717114849182</v>
       </c>
       <c r="C91">
-        <v>-17.4271078770183</v>
+        <v>-17.81335958118346</v>
       </c>
       <c r="D91">
-        <v>9.0738921229817</v>
+        <v>8.996640418816542</v>
       </c>
       <c r="E91">
-        <v>16.201</v>
+        <v>16.51</v>
       </c>
       <c r="F91">
-        <v>27.501</v>
+        <v>27.81</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -8749,37 +8749,37 @@
         <v>1.45</v>
       </c>
       <c r="M91">
-        <v>6.4847358</v>
+        <v>6.557598</v>
       </c>
       <c r="N91">
-        <v>-5.0347358</v>
+        <v>-5.107598000000001</v>
       </c>
       <c r="O91">
-        <v>-1.611115456</v>
+        <v>-1.63443136</v>
       </c>
       <c r="P91">
-        <v>-3.423620344</v>
+        <v>-3.473166640000001</v>
       </c>
       <c r="Q91">
-        <v>-0.9936203439999995</v>
+        <v>-1.04316664</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.656599024679015</v>
+        <v>0.7176789271469165</v>
       </c>
       <c r="T91">
-        <v>7.96075887403098</v>
+        <v>8.756834761434078</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0715526452133948</v>
+        <v>0.07075761582213486</v>
       </c>
       <c r="W91">
-        <v>0.2189278862586815</v>
+        <v>0.2191153541891406</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2236020162918588</v>
+        <v>0.2211175494441714</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2689717114849182</v>
+        <v>0.2708717114849182</v>
       </c>
       <c r="C92">
-        <v>-17.81335958118346</v>
+        <v>-18.19830700559756</v>
       </c>
       <c r="D92">
-        <v>8.996640418816542</v>
+        <v>8.920692994402449</v>
       </c>
       <c r="E92">
-        <v>16.51</v>
+        <v>16.819</v>
       </c>
       <c r="F92">
-        <v>27.81</v>
+        <v>28.119</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -8831,37 +8831,37 @@
         <v>1.45</v>
       </c>
       <c r="M92">
-        <v>6.557598</v>
+        <v>6.630460200000001</v>
       </c>
       <c r="N92">
-        <v>-5.107598000000001</v>
+        <v>-5.180460200000001</v>
       </c>
       <c r="O92">
-        <v>-1.63443136</v>
+        <v>-1.657747264</v>
       </c>
       <c r="P92">
-        <v>-3.473166640000001</v>
+        <v>-3.522712936</v>
       </c>
       <c r="Q92">
-        <v>-1.04316664</v>
+        <v>-1.092712936</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7176789271469165</v>
+        <v>0.7923321412743518</v>
       </c>
       <c r="T92">
-        <v>8.756834761434078</v>
+        <v>9.729816401593421</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07075761582213486</v>
+        <v>0.0699800596043092</v>
       </c>
       <c r="W92">
-        <v>0.2191153541891406</v>
+        <v>0.2192987019453039</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2211175494441714</v>
+        <v>0.2186876862634664</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2708717114849182</v>
+        <v>0.2727717114849182</v>
       </c>
       <c r="C93">
-        <v>-18.19830700559756</v>
+        <v>-18.58198290497937</v>
       </c>
       <c r="D93">
-        <v>8.920692994402449</v>
+        <v>8.846017095020638</v>
       </c>
       <c r="E93">
-        <v>16.819</v>
+        <v>17.128</v>
       </c>
       <c r="F93">
-        <v>28.119</v>
+        <v>28.428</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -8913,37 +8913,37 @@
         <v>1.45</v>
       </c>
       <c r="M93">
-        <v>6.630460200000001</v>
+        <v>6.703322400000001</v>
       </c>
       <c r="N93">
-        <v>-5.180460200000001</v>
+        <v>-5.253322400000002</v>
       </c>
       <c r="O93">
-        <v>-1.657747264</v>
+        <v>-1.681063168000001</v>
       </c>
       <c r="P93">
-        <v>-3.522712936</v>
+        <v>-3.572259232000001</v>
       </c>
       <c r="Q93">
-        <v>-1.092712936</v>
+        <v>-1.142259232000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7923321412743518</v>
+        <v>0.8856486589336459</v>
       </c>
       <c r="T93">
-        <v>9.729816401593421</v>
+        <v>10.9460434517926</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0699800596043092</v>
+        <v>0.06921940678252322</v>
       </c>
       <c r="W93">
-        <v>0.2192987019453039</v>
+        <v>0.219478063880681</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2186876862634664</v>
+        <v>0.216310646195385</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2727717114849182</v>
+        <v>0.2746717114849182</v>
       </c>
       <c r="C94">
-        <v>-18.58198290497937</v>
+        <v>-18.96441894638218</v>
       </c>
       <c r="D94">
-        <v>8.846017095020638</v>
+        <v>8.772581053617824</v>
       </c>
       <c r="E94">
-        <v>17.128</v>
+        <v>17.437</v>
       </c>
       <c r="F94">
-        <v>28.428</v>
+        <v>28.737</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -8995,37 +8995,37 @@
         <v>1.45</v>
       </c>
       <c r="M94">
-        <v>6.703322400000001</v>
+        <v>6.776184600000001</v>
       </c>
       <c r="N94">
-        <v>-5.253322400000002</v>
+        <v>-5.326184600000001</v>
       </c>
       <c r="O94">
-        <v>-1.681063168000001</v>
+        <v>-1.704379072</v>
       </c>
       <c r="P94">
-        <v>-3.572259232000001</v>
+        <v>-3.621805528000001</v>
       </c>
       <c r="Q94">
-        <v>-1.142259232000001</v>
+        <v>-1.191805528000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8856486589336459</v>
+        <v>1.00562703878131</v>
       </c>
       <c r="T94">
-        <v>10.9460434517926</v>
+        <v>12.50976394490583</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06921940678252322</v>
+        <v>0.06847511208593696</v>
       </c>
       <c r="W94">
-        <v>0.219478063880681</v>
+        <v>0.2196535685701361</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.216310646195385</v>
+        <v>0.2139847252685529</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2746717114849182</v>
+        <v>0.2765717114849182</v>
       </c>
       <c r="C95">
-        <v>-18.96441894638218</v>
+        <v>-19.34564575396887</v>
       </c>
       <c r="D95">
-        <v>8.772581053617824</v>
+        <v>8.700354246031129</v>
       </c>
       <c r="E95">
-        <v>17.437</v>
+        <v>17.746</v>
       </c>
       <c r="F95">
-        <v>28.737</v>
+        <v>29.046</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -9077,37 +9077,37 @@
         <v>1.45</v>
       </c>
       <c r="M95">
-        <v>6.776184600000001</v>
+        <v>6.849046800000001</v>
       </c>
       <c r="N95">
-        <v>-5.326184600000001</v>
+        <v>-5.399046800000001</v>
       </c>
       <c r="O95">
-        <v>-1.704379072</v>
+        <v>-1.727694976</v>
       </c>
       <c r="P95">
-        <v>-3.621805528000001</v>
+        <v>-3.671351824</v>
       </c>
       <c r="Q95">
-        <v>-1.191805528000001</v>
+        <v>-1.241351824</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.00562703878131</v>
+        <v>1.165598211911529</v>
       </c>
       <c r="T95">
-        <v>12.50976394490583</v>
+        <v>14.59472460239014</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06847511208593696</v>
+        <v>0.06774665344672486</v>
       </c>
       <c r="W95">
-        <v>0.2196535685701361</v>
+        <v>0.2198253391172623</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2139847252685529</v>
+        <v>0.2117082920210153</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2765717114849182</v>
+        <v>0.2784717114849182</v>
       </c>
       <c r="C96">
-        <v>-19.34564575396887</v>
+        <v>-19.7256929515932</v>
       </c>
       <c r="D96">
-        <v>8.700354246031129</v>
+        <v>8.629307048406801</v>
       </c>
       <c r="E96">
-        <v>17.746</v>
+        <v>18.055</v>
       </c>
       <c r="F96">
-        <v>29.046</v>
+        <v>29.355</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -9159,37 +9159,37 @@
         <v>1.45</v>
       </c>
       <c r="M96">
-        <v>6.849046800000001</v>
+        <v>6.921909000000001</v>
       </c>
       <c r="N96">
-        <v>-5.399046800000001</v>
+        <v>-5.471909000000002</v>
       </c>
       <c r="O96">
-        <v>-1.727694976</v>
+        <v>-1.751010880000001</v>
       </c>
       <c r="P96">
-        <v>-3.671351824</v>
+        <v>-3.720898120000001</v>
       </c>
       <c r="Q96">
-        <v>-1.241351824</v>
+        <v>-1.290898120000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.165598211911529</v>
+        <v>1.389557854293835</v>
       </c>
       <c r="T96">
-        <v>14.59472460239014</v>
+        <v>17.51366952286818</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06774665344672486</v>
+        <v>0.06703353077886459</v>
       </c>
       <c r="W96">
-        <v>0.2198253391172623</v>
+        <v>0.2199934934423438</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2117082920210153</v>
+        <v>0.2094797836839518</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2784717114849182</v>
+        <v>0.2803717114849182</v>
       </c>
       <c r="C97">
-        <v>-19.7256929515932</v>
+        <v>-20.10458920331163</v>
       </c>
       <c r="D97">
-        <v>8.629307048406801</v>
+        <v>8.559410796688372</v>
       </c>
       <c r="E97">
-        <v>18.055</v>
+        <v>18.364</v>
       </c>
       <c r="F97">
-        <v>29.355</v>
+        <v>29.66400000000001</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -9241,37 +9241,37 @@
         <v>1.45</v>
       </c>
       <c r="M97">
-        <v>6.921909000000001</v>
+        <v>6.994771200000002</v>
       </c>
       <c r="N97">
-        <v>-5.471909000000002</v>
+        <v>-5.544771200000001</v>
       </c>
       <c r="O97">
-        <v>-1.751010880000001</v>
+        <v>-1.774326784000001</v>
       </c>
       <c r="P97">
-        <v>-3.720898120000001</v>
+        <v>-3.770444416000001</v>
       </c>
       <c r="Q97">
-        <v>-1.290898120000001</v>
+        <v>-1.340444416000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.389557854293835</v>
+        <v>1.725497317867294</v>
       </c>
       <c r="T97">
-        <v>17.51366952286818</v>
+        <v>21.89208690358523</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06703353077886459</v>
+        <v>0.06633526483325142</v>
       </c>
       <c r="W97">
-        <v>0.2199934934423438</v>
+        <v>0.2201581445523193</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2094797836839518</v>
+        <v>0.2072977026039108</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2803717114849182</v>
+        <v>0.2822717114849182</v>
       </c>
       <c r="C98">
-        <v>-20.10458920331163</v>
+        <v>-20.48236225194221</v>
       </c>
       <c r="D98">
-        <v>8.559410796688374</v>
+        <v>8.490637748057795</v>
       </c>
       <c r="E98">
-        <v>18.364</v>
+        <v>18.673</v>
       </c>
       <c r="F98">
-        <v>29.664</v>
+        <v>29.973</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -9323,37 +9323,37 @@
         <v>1.45</v>
       </c>
       <c r="M98">
-        <v>6.994771200000001</v>
+        <v>7.067633400000001</v>
       </c>
       <c r="N98">
-        <v>-5.544771200000001</v>
+        <v>-5.617633400000001</v>
       </c>
       <c r="O98">
-        <v>-1.774326784000001</v>
+        <v>-1.797642688</v>
       </c>
       <c r="P98">
-        <v>-3.770444416000001</v>
+        <v>-3.819990712000001</v>
       </c>
       <c r="Q98">
-        <v>-1.340444416000001</v>
+        <v>-1.389990712</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.72549731786729</v>
+        <v>2.285396423823053</v>
       </c>
       <c r="T98">
-        <v>21.89208690358517</v>
+        <v>29.18944920478024</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06633526483325143</v>
+        <v>0.06565139612363027</v>
       </c>
       <c r="W98">
-        <v>0.2201581445523193</v>
+        <v>0.220319400794048</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2072977026039107</v>
+        <v>0.2051606128863447</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2822717114849182</v>
+        <v>0.2841717114849182</v>
       </c>
       <c r="C99">
-        <v>-20.48236225194221</v>
+        <v>-20.85903895577931</v>
       </c>
       <c r="D99">
-        <v>8.490637748057795</v>
+        <v>8.422961044220688</v>
       </c>
       <c r="E99">
-        <v>18.673</v>
+        <v>18.982</v>
       </c>
       <c r="F99">
-        <v>29.973</v>
+        <v>30.282</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -9405,37 +9405,37 @@
         <v>1.45</v>
       </c>
       <c r="M99">
-        <v>7.067633400000001</v>
+        <v>7.1404956</v>
       </c>
       <c r="N99">
-        <v>-5.617633400000001</v>
+        <v>-5.6904956</v>
       </c>
       <c r="O99">
-        <v>-1.797642688</v>
+        <v>-1.820958592</v>
       </c>
       <c r="P99">
-        <v>-3.819990712000001</v>
+        <v>-3.869537008</v>
       </c>
       <c r="Q99">
-        <v>-1.389990712</v>
+        <v>-1.439537008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.285396423823053</v>
+        <v>3.405194635734579</v>
       </c>
       <c r="T99">
-        <v>29.18944920478024</v>
+        <v>43.78417380717035</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06565139612363027</v>
+        <v>0.06498148391828712</v>
       </c>
       <c r="W99">
-        <v>0.220319400794048</v>
+        <v>0.2204773660920679</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2051606128863447</v>
+        <v>0.2030671372446473</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2841717114849182</v>
+        <v>0.2860717114849182</v>
       </c>
       <c r="C100">
-        <v>-20.85903895577931</v>
+        <v>-21.23464532356649</v>
       </c>
       <c r="D100">
-        <v>8.422961044220688</v>
+        <v>8.356354676433508</v>
       </c>
       <c r="E100">
-        <v>18.982</v>
+        <v>19.291</v>
       </c>
       <c r="F100">
-        <v>30.282</v>
+        <v>30.591</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -9487,37 +9487,37 @@
         <v>1.45</v>
       </c>
       <c r="M100">
-        <v>7.1404956</v>
+        <v>7.213357800000001</v>
       </c>
       <c r="N100">
-        <v>-5.6904956</v>
+        <v>-5.763357800000001</v>
       </c>
       <c r="O100">
-        <v>-1.820958592</v>
+        <v>-1.844274496000001</v>
       </c>
       <c r="P100">
-        <v>-3.869537008</v>
+        <v>-3.919083304000001</v>
       </c>
       <c r="Q100">
-        <v>-1.439537008</v>
+        <v>-1.489083304000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.405194635734579</v>
+        <v>6.764589271469159</v>
       </c>
       <c r="T100">
-        <v>43.78417380717035</v>
+        <v>87.56834761434069</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06498148391828712</v>
+        <v>0.06432510529284986</v>
       </c>
       <c r="W100">
-        <v>0.2204773660920679</v>
+        <v>0.220632140171946</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2030671372446473</v>
+        <v>0.2010159540401558</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2860717114849182</v>
-      </c>
-      <c r="C101">
-        <v>-21.23464532356649</v>
-      </c>
-      <c r="D101">
-        <v>8.356354676433508</v>
-      </c>
-      <c r="E101">
-        <v>19.291</v>
-      </c>
-      <c r="F101">
-        <v>30.591</v>
-      </c>
-      <c r="G101">
-        <v>1</v>
-      </c>
-      <c r="H101">
-        <v>19.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.88</v>
-      </c>
-      <c r="K101">
-        <v>2.43</v>
-      </c>
-      <c r="L101">
-        <v>1.45</v>
-      </c>
-      <c r="M101">
-        <v>7.213357800000001</v>
-      </c>
-      <c r="N101">
-        <v>-5.763357800000001</v>
-      </c>
-      <c r="O101">
-        <v>-1.844274496000001</v>
-      </c>
-      <c r="P101">
-        <v>-3.919083304000001</v>
-      </c>
-      <c r="Q101">
-        <v>-1.489083304000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.764589271469159</v>
-      </c>
-      <c r="T101">
-        <v>87.56834761434069</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06432510529284986</v>
-      </c>
-      <c r="W101">
-        <v>0.220632140171946</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2010159540401558</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
